--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,40 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC0B01-8EFD-4F4C-AEC0-DB67472EEF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -50,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -120,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2">
+    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -147,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -206,56 +199,53 @@
     <t>playType</t>
   </si>
   <si>
-    <t>[{18,[{2,8},{5,10},{10,1},{15,8},{20,10},{25,12},{50,10},{100,1},{200,1},{500,1},{1000,1},{3333,1},{5000,1},{10000,1}]}]</t>
-  </si>
-  <si>
     <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
   </si>
   <si>
     <t>数字符号指定元素本身每次出现随机的倍数金额</t>
   </si>
   <si>
-    <t>[[{18,[1,2,3,4]},{16,[5]}],0,16]</t>
-  </si>
-  <si>
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>[{1,18,0,10000,150,10010005}]</t>
-  </si>
-  <si>
-    <t>投资，[任务类型 ,收集元素, 起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
-  </si>
-  <si>
     <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010009]</t>
   </si>
   <si>
     <t>收集已解锁的地图，[任务类型 ,{收集场景ID, 起始值,收集的目标个数},{收集元素ID, 起始值,收集的目标个数},奖励小游戏ID]</t>
   </si>
   <si>
-    <t>[[{18,[1,2,3,4]},{15,[5]}],0,15]</t>
-  </si>
-  <si>
     <t>黄金列车收集现金奖励，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>[10000]</t>
-  </si>
-  <si>
-    <t>[单线押分值],当前档位低于此值不开启收集功能</t>
+    <t>[{1,18,10000,0,10000,150,10010005}]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) 起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,1&amp;2&amp;3&amp;4;16,5;0;16</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,1&amp;2&amp;3&amp;4;15,5;0;15</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,2&amp;8-5&amp;10-10&amp;1-15&amp;8-20&amp;10-25&amp;12-50&amp;10-100&amp;1-200&amp;1-500&amp;1-1000&amp;1-3333&amp;1-5000&amp;1-10000&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,157 +283,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -454,202 +293,30 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -657,327 +324,40 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
-    <cellStyle name="常规 80" xfId="50"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -986,6 +366,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1250,21 +633,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
     <col min="8" max="8" width="33.875" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1324,7 +709,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,11 +731,13 @@
       <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="H3" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1362,7 +749,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1384,17 +771,17 @@
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1416,17 +803,17 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>22</v>
+      <c r="H6" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1448,17 +835,17 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>24</v>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1481,16 +868,16 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1510,58 +897,26 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>100100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B1:B4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC0B01-8EFD-4F4C-AEC0-DB67472EEF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF2ED1E-0086-45D5-A96F-490264BCB50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,6 +33,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1.普通
@@ -49,6 +50,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0表示包含所有模式</t>
@@ -61,6 +63,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -120,6 +123,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -128,6 +132,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -135,12 +140,15 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{499C2E6F-D958-4E42-BA1D-556ACAF22B31}">
+      <text/>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -202,9 +210,6 @@
     <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
   </si>
   <si>
-    <t>数字符号指定元素本身每次出现随机的倍数金额</t>
-  </si>
-  <si>
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
@@ -215,14 +220,6 @@
   </si>
   <si>
     <t>黄金列车收集现金奖励，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
-  </si>
-  <si>
-    <t>[{1,18,10000,0,10000,150,10010005}]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) 起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>18,1&amp;2&amp;3&amp;4;16,5;0;16</t>
@@ -238,6 +235,26 @@
   </si>
   <si>
     <t>18,2&amp;8-5&amp;10-10&amp;1-15&amp;8-20&amp;10-25&amp;12-50&amp;10-100&amp;1-200&amp;1-500&amp;1-1000&amp;1-3333&amp;1-5000&amp;1-10000&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字符号指定元素本身每次出现随机的倍数金额</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,20&amp;8-50&amp;10-100&amp;1-150&amp;8-200&amp;10-250&amp;12-500&amp;10-1000&amp;1-2000&amp;1-5000&amp;1-10000&amp;1-33330&amp;1-50000&amp;1-100000&amp;1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金列车触发局结果生成倍数，数字符号指定元素本身每次出现随机的倍数金额</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,18,10000,0,10000,150,10010005</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -257,40 +274,47 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -639,12 +663,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="33.875" customWidth="1"/>
+    <col min="8" max="8" width="53.25" customWidth="1"/>
     <col min="9" max="9" width="18.75" customWidth="1"/>
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
@@ -732,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -772,13 +796,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -804,13 +828,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -835,14 +859,14 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>25</v>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>26</v>
+      <c r="J7" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -868,13 +892,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -900,13 +924,45 @@
         <v>4</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF2ED1E-0086-45D5-A96F-490264BCB50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE607D56-700F-4529-A40D-8BB31D86BD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1,18,10000,0,10000,150,10010005</t>
+    <t>1,18,100,0,10000,10,10010005</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE607D56-700F-4529-A40D-8BB31D86BD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF721190-BFDC-46D2-B166-87C38AE8DEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>1,18,100,0,10000,10,10010005</t>
+    <t>1,18,100,0,10000,40,10010005</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF721190-BFDC-46D2-B166-87C38AE8DEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DA14AF-768A-4ACA-96B2-E277176EFA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,10 +242,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>15,20&amp;8-50&amp;10-100&amp;1-150&amp;8-200&amp;10-250&amp;12-500&amp;10-1000&amp;1-2000&amp;1-5000&amp;1-10000&amp;1-33330&amp;1-50000&amp;1-100000&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>黄金列车触发局结果生成倍数，数字符号指定元素本身每次出现随机的倍数金额</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -255,6 +251,10 @@
   </si>
   <si>
     <t>1,18,100,0,10000,40,10010005</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,20&amp;8-50&amp;10-100&amp;1-150&amp;8-200&amp;10-250&amp;12-500&amp;10-1000&amp;1-2000&amp;1-5000&amp;1-10000&amp;1-33330&amp;1-50000&amp;1-100000&amp;1;10010006</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -668,7 +668,7 @@
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="53.25" customWidth="1"/>
+    <col min="8" max="8" width="73.375" customWidth="1"/>
     <col min="9" max="9" width="18.75" customWidth="1"/>
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
@@ -860,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
@@ -956,13 +956,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,39 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DA14AF-768A-4ACA-96B2-E277176EFA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
+    <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1.普通
@@ -44,26 +51,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0表示包含所有模式</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -116,14 +121,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -132,7 +136,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -140,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{499C2E6F-D958-4E42-BA1D-556ACAF22B31}">
+    <comment ref="G1" authorId="0">
       <text/>
     </comment>
   </commentList>
@@ -148,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -207,62 +210,275 @@
     <t>playType</t>
   </si>
   <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>18,5&amp;7000-8&amp;8000-10&amp;2500-12&amp;3000-15&amp;1000-18&amp;800-20&amp;500-25&amp;150-30&amp;50-35&amp;10-40&amp;1</t>
+  </si>
+  <si>
     <t>&lt;&lt;"美元快递"/utf8&gt;&gt;</t>
   </si>
   <si>
+    <t>数字符号指定元素本身每次出现随机的倍数金额</t>
+  </si>
+  <si>
+    <t>18,1&amp;2&amp;3&amp;4;16,5;0;16</t>
+  </si>
+  <si>
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
+    <t>1,18,400,0,10000,150,10010005</t>
+  </si>
+  <si>
+    <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
+  </si>
+  <si>
     <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010009]</t>
   </si>
   <si>
     <t>收集已解锁的地图，[任务类型 ,{收集场景ID, 起始值,收集的目标个数},{收集元素ID, 起始值,收集的目标个数},奖励小游戏ID]</t>
   </si>
   <si>
+    <t>18,1&amp;2&amp;3&amp;4;15,5;0;15</t>
+  </si>
+  <si>
     <t>黄金列车收集现金奖励，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>18,1&amp;2&amp;3&amp;4;16,5;0;16</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>value</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,1&amp;2&amp;3&amp;4;15,5;0;15</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>18,2&amp;8-5&amp;10-10&amp;1-15&amp;8-20&amp;10-25&amp;12-50&amp;10-100&amp;1-200&amp;1-500&amp;1-1000&amp;1-3333&amp;1-5000&amp;1-10000&amp;1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数字符号指定元素本身每次出现随机的倍数金额</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄金列车触发局结果生成倍数，数字符号指定元素本身每次出现随机的倍数金额</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,18,100,0,10000,40,10010005</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,20&amp;8-50&amp;10-100&amp;1-150&amp;8-200&amp;10-250&amp;12-500&amp;10-1000&amp;1-2000&amp;1-5000&amp;1-10000&amp;1-33330&amp;1-50000&amp;1-100000&amp;1;10010006</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010006</t>
+  </si>
+  <si>
+    <t>黄金列车触发局结果生成倍数，数字符号指定元素本身每次出现随机的倍数金额，元素ID,倍数&amp;权重;小游戏ID</t>
+  </si>
+  <si>
+    <t>18,5&amp;11000-8&amp;8000-10&amp;2500-12&amp;1000-15&amp;800-18&amp;500-20&amp;150-25&amp;50</t>
+  </si>
+  <si>
+    <t>18,5&amp;12000-8&amp;8000-10&amp;2500-12&amp;1000-15&amp;800-18&amp;500-20&amp;150-25&amp;5</t>
+  </si>
+  <si>
+    <t>18,5&amp;15000-8&amp;8000-10&amp;2500-12&amp;1000-15&amp;800-18&amp;500-20&amp;100-25&amp;1</t>
+  </si>
+  <si>
+    <t>18,5&amp;15000-8&amp;9000-10&amp;2500-12&amp;800-15&amp;200-18&amp;50-20&amp;1</t>
+  </si>
+  <si>
+    <t>18,5&amp;15000-8&amp;8000-10&amp;2500-12&amp;100-15&amp;50-18&amp;1</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010036]</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010037]</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010038]</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010039]</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010040]</t>
+  </si>
+  <si>
+    <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010041]</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010012</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010013</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010014</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010015</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010016</t>
+  </si>
+  <si>
+    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010017</t>
+  </si>
+  <si>
+    <t>特殊玩法</t>
+  </si>
+  <si>
+    <t>typeID</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>随机倍数</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>元素收集奖励，美元快递现金收集</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>收集元素送小游戏</t>
+  </si>
+  <si>
+    <t>免费</t>
+  </si>
+  <si>
+    <t>收集不同场景，美元快递地图集齐送黄金列车</t>
+  </si>
+  <si>
+    <t>重转</t>
+  </si>
+  <si>
+    <t>元素收集奖励1，美元快递现金收集</t>
+  </si>
+  <si>
+    <t>选择标识</t>
+  </si>
+  <si>
+    <t>黄金列车结果库生成倍数</t>
+  </si>
+  <si>
+    <t>扩展旋转</t>
+  </si>
+  <si>
+    <t>通用免费1</t>
+  </si>
+  <si>
+    <t>通用免费2</t>
+  </si>
+  <si>
+    <t>通用免费3</t>
+  </si>
+  <si>
+    <t>通用免费4</t>
+  </si>
+  <si>
+    <t>通用免费5</t>
+  </si>
+  <si>
+    <t>通用免费6</t>
+  </si>
+  <si>
+    <t>通用免费7</t>
+  </si>
+  <si>
+    <t>通用免费8</t>
+  </si>
+  <si>
+    <t>通用免费9</t>
+  </si>
+  <si>
+    <t>通用免费10</t>
+  </si>
+  <si>
+    <t>通用免费11</t>
+  </si>
+  <si>
+    <t>通用免费12</t>
+  </si>
+  <si>
+    <t>通用免费13</t>
+  </si>
+  <si>
+    <t>通用免费14</t>
+  </si>
+  <si>
+    <t>通用免费15</t>
+  </si>
+  <si>
+    <t>通用免费16</t>
+  </si>
+  <si>
+    <t>免费1</t>
+  </si>
+  <si>
+    <t>通用重转1</t>
+  </si>
+  <si>
+    <t>通用重转2</t>
+  </si>
+  <si>
+    <t>通用重转3</t>
+  </si>
+  <si>
+    <t>通用重转4</t>
+  </si>
+  <si>
+    <t>通用重转5</t>
+  </si>
+  <si>
+    <t>通用重转6</t>
+  </si>
+  <si>
+    <t>通用重转7</t>
+  </si>
+  <si>
+    <t>通用重转8</t>
+  </si>
+  <si>
+    <t>通用重转9</t>
+  </si>
+  <si>
+    <t>通用重转10</t>
+  </si>
+  <si>
+    <t>通用重转11</t>
+  </si>
+  <si>
+    <t>通用重转12</t>
+  </si>
+  <si>
+    <t>通用普通1</t>
+  </si>
+  <si>
+    <t>通用普通2</t>
+  </si>
+  <si>
+    <t>通用普通3</t>
+  </si>
+  <si>
+    <t>通用普通4</t>
+  </si>
+  <si>
+    <t>通用普通5</t>
+  </si>
+  <si>
+    <t>通用普通6</t>
+  </si>
+  <si>
+    <t>通用普通7</t>
+  </si>
+  <si>
+    <t>通用普通8</t>
+  </si>
+  <si>
+    <t>通用普通9</t>
+  </si>
+  <si>
+    <t>通用普通10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,73 +490,375 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -348,40 +866,324 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 80" xfId="50"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -391,18 +1193,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,23 +1449,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="73.375" customWidth="1"/>
+    <col min="8" max="8" width="53.25" customWidth="1"/>
     <col min="9" max="9" width="18.75" customWidth="1"/>
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +1497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -718,10 +1510,10 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -733,7 +1525,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" hidden="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,22 +1538,22 @@
       <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>25</v>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" hidden="1" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -773,7 +1565,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -784,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -795,17 +1587,17 @@
       <c r="G5" s="1">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -827,17 +1619,17 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -860,16 +1652,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -880,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -892,16 +1684,16 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -923,17 +1715,17 @@
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>19</v>
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -956,23 +1748,1037 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="4" t="s">
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:10">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:10">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:10">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:10">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>6</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>29</v>
+      <c r="B23" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:10">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:10">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:10">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:10">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:10">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" s="1">
+        <v>100100</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>5</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B1:B4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,41 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61056B0-9B13-4345-9CEE-C3C7875B4827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="32265" yWindow="1680" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +44,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2">
+    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -143,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text/>
     </comment>
   </commentList>
@@ -228,9 +221,6 @@
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>1,18,400,0,10000,150,10010005</t>
-  </si>
-  <si>
     <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
   </si>
   <si>
@@ -466,19 +456,17 @@
   </si>
   <si>
     <t>通用普通10</t>
+  </si>
+  <si>
+    <t>1,18,400,0,10000,105,10010005</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,156 +492,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -663,202 +509,36 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -866,324 +546,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
-    <cellStyle name="常规 80" xfId="50"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1192,6 +585,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1449,14 +845,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
@@ -1465,7 +861,7 @@
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1525,7 +921,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:10">
+    <row r="3" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +949,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:10">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1565,7 +961,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1597,7 +993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1629,7 +1025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1651,17 +1047,17 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1684,16 +1080,16 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1716,16 +1112,16 @@
         <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1748,16 +1144,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1780,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>21</v>
@@ -1789,7 +1185,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1812,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>21</v>
@@ -1821,7 +1217,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1844,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>21</v>
@@ -1853,7 +1249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1876,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>21</v>
@@ -1885,7 +1281,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1908,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -1917,7 +1313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1940,7 +1336,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -1949,7 +1345,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:10">
+    <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1972,16 +1368,16 @@
         <v>3</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -2004,16 +1400,16 @@
         <v>3</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2036,16 +1432,16 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2068,16 +1464,16 @@
         <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2100,16 +1496,16 @@
         <v>3</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2132,16 +1528,16 @@
         <v>3</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2164,16 +1560,16 @@
         <v>5</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2196,16 +1592,16 @@
         <v>5</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2228,16 +1624,16 @@
         <v>5</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2260,16 +1656,16 @@
         <v>5</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2292,16 +1688,16 @@
         <v>5</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2324,461 +1720,460 @@
         <v>5</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="B1:B4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>53</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>55</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61056B0-9B13-4345-9CEE-C3C7875B4827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D55E647-D62F-46E9-9CF8-B0B70B810C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32265" yWindow="1680" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1.普通
@@ -50,6 +51,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0表示包含所有模式</t>
@@ -62,6 +64,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -121,6 +124,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -129,6 +133,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -458,7 +463,7 @@
     <t>通用普通10</t>
   </si>
   <si>
-    <t>1,18,400,0,10000,105,10010005</t>
+    <t>1,18,400,0,10000,16,10010005</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -466,7 +471,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,49 +483,49 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -552,7 +557,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -561,9 +566,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1047,7 +1049,7 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="1" t="s">
         <v>104</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -2173,7 +2175,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,40 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D55E647-D62F-46E9-9CF8-B0B70B810C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1.普通
@@ -45,26 +51,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="D1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>0表示包含所有模式</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">0 全部 
@@ -117,14 +121,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F1" authorId="2">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>po5lichaoqun:</t>
@@ -133,7 +136,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -141,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="G1" authorId="0">
       <text/>
     </comment>
   </commentList>
@@ -149,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -226,6 +228,9 @@
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
+    <t>1,18,400,0,10000,150,10010005</t>
+  </si>
+  <si>
     <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
   </si>
   <si>
@@ -241,7 +246,7 @@
     <t>黄金列车收集现金奖励，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010006</t>
+    <t>15,5&amp;3200-8&amp;2200-10&amp;1800-15&amp;1000-18&amp;500-20&amp;250-25&amp;200-30&amp;150-35&amp;50-40&amp;25-50&amp;10-80&amp;5-100&amp;1;10010006</t>
   </si>
   <si>
     <t>黄金列车触发局结果生成倍数，数字符号指定元素本身每次出现随机的倍数金额，元素ID,倍数&amp;权重;小游戏ID</t>
@@ -280,22 +285,13 @@
     <t>[1,{[1,2,3,4,5,6,7,8], 0,8},{18, 0,1200},10010041]</t>
   </si>
   <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010012</t>
-  </si>
-  <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010013</t>
-  </si>
-  <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010014</t>
-  </si>
-  <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010015</t>
-  </si>
-  <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010016</t>
-  </si>
-  <si>
-    <t>15,15&amp;1000-18&amp;800-20&amp;500-25&amp;250-30&amp;150-35&amp;80-40&amp;50-50&amp;25-80&amp;10-100&amp;1;10010017</t>
+    <t>15,3&amp;3500-5&amp;3200-8&amp;2200-10&amp;1800-15&amp;500-18&amp;100-20&amp;50-25&amp;25-30&amp;0-35&amp;0;10010012</t>
+  </si>
+  <si>
+    <t>15,3&amp;3500-5&amp;2800-8&amp;2200-10&amp;200-15&amp;50-18&amp;8-20&amp;1;10010012</t>
+  </si>
+  <si>
+    <t>15,5&amp;3200-8&amp;1200;10010014</t>
   </si>
   <si>
     <t>特殊玩法</t>
@@ -461,17 +457,19 @@
   </si>
   <si>
     <t>通用普通10</t>
-  </si>
-  <si>
-    <t>1,18,400,0,10000,16,10010005</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -483,67 +481,375 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -551,34 +857,324 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 80" xfId="50"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -587,9 +1183,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -847,14 +1440,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
@@ -863,7 +1456,7 @@
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +1488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -923,7 +1516,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" hidden="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +1544,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" hidden="1" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -963,7 +1556,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -995,7 +1588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1027,7 +1620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1050,16 +1643,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1082,16 +1675,16 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1114,16 +1707,16 @@
         <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1134,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1146,16 +1739,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1178,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>21</v>
@@ -1187,7 +1780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1210,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>21</v>
@@ -1219,7 +1812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" ht="16.5" spans="1:10">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1242,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>21</v>
@@ -1251,7 +1844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" ht="16.5" spans="1:10">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1274,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>21</v>
@@ -1283,7 +1876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" ht="16.5" spans="1:10">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1306,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -1315,7 +1908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" ht="16.5" spans="1:10">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1338,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -1347,7 +1940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" ht="16.5" spans="1:10">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1370,16 +1963,16 @@
         <v>3</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:10">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1402,16 +1995,16 @@
         <v>3</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1434,16 +2027,16 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:10">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1466,16 +2059,16 @@
         <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:10">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1498,16 +2091,16 @@
         <v>3</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:10">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1530,16 +2123,16 @@
         <v>3</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:10">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1550,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -1562,16 +2155,16 @@
         <v>5</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1582,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -1594,16 +2187,16 @@
         <v>5</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:10">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1614,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -1626,16 +2219,16 @@
         <v>5</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:10">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1646,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -1664,10 +2257,10 @@
         <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:10">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1678,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -1690,16 +2283,16 @@
         <v>5</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:10">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1710,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -1722,460 +2315,461 @@
         <v>5</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="B1:B4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -1,41 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDDDBD7-81B4-4BE8-9CBF-B5BE3E574BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="31950" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
     <sheet name="desc" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
     <author>po5lichaoqun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +44,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="1">
+    <comment ref="D1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="2">
+    <comment ref="F1" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -143,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text/>
     </comment>
   </commentList>
@@ -228,9 +221,6 @@
     <t>美元现金，[[{触发元素,[触发列]}],是否继承,收集元素]</t>
   </si>
   <si>
-    <t>1,18,400,0,10000,150,10010005</t>
-  </si>
-  <si>
     <t>投资，[任务类型 ,收集元素,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
   </si>
   <si>
@@ -457,19 +447,17 @@
   </si>
   <si>
     <t>通用普通10</t>
+  </si>
+  <si>
+    <t>1,18,400,0,10000,16,10010005</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,156 +483,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -654,202 +500,36 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -857,324 +537,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="51">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="51">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
-    <cellStyle name="常规 80" xfId="50"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 80" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1183,6 +576,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1440,14 +836,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
@@ -1456,7 +852,7 @@
     <col min="10" max="10" width="89.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1516,7 +912,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1544,7 +940,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1556,7 +952,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1588,7 +984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1620,7 +1016,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1642,17 +1038,17 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1675,16 +1071,16 @@
         <v>3</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1707,16 +1103,16 @@
         <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1739,16 +1135,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1771,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>21</v>
@@ -1780,7 +1176,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1803,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>21</v>
@@ -1812,7 +1208,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1835,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>21</v>
@@ -1844,7 +1240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1867,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>21</v>
@@ -1876,7 +1272,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1899,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -1908,7 +1304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1931,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -1940,7 +1336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:10">
+    <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1963,16 +1359,16 @@
         <v>3</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1995,16 +1391,16 @@
         <v>3</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -2027,16 +1423,16 @@
         <v>3</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -2059,16 +1455,16 @@
         <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -2091,16 +1487,16 @@
         <v>3</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -2123,16 +1519,16 @@
         <v>3</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2155,16 +1551,16 @@
         <v>5</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -2187,16 +1583,16 @@
         <v>5</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -2219,16 +1615,16 @@
         <v>5</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -2251,16 +1647,16 @@
         <v>5</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2283,16 +1679,16 @@
         <v>5</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2315,461 +1711,460 @@
         <v>5</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="B1:B4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>50</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>52</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
       <c r="B23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -212,7 +212,7 @@
     <t>最右侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1_2014001_1|2_2014001_2|3_2014001_3|4_2014001_4|5_2014001_5|6_2014001_6|7_2014002_7|8_2014003_8</t>
+    <t>1_2014004_1|2_2014005_2|3_2014006_3|4_2014007_4|5_2014008_5|6_2014009_6|7_2014010_7|8_2014011_8</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -567,17 +567,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -146,7 +146,7 @@
     <t>全局累计：收集元素送小游戏，当场上有目标图案时，收集图案累积图案出现次数，达到条件后触发小游戏</t>
   </si>
   <si>
-    <t>18,400,0,10000,150,30010010</t>
+    <t>18,20,0,10000,150,30010010</t>
   </si>
   <si>
     <t>收集图案ID,单线押分(低于此值不开启收集功能) ,起始值,收集概率,收集的目标个数 ,奖励的小游戏id]</t>
@@ -170,7 +170,7 @@
     <t>储存的平均押分：用于黄金列车、投资游戏中的奖金计算，从进X局下注中取平均值，需要区分倍场，每个倍场独立存1个</t>
   </si>
   <si>
-    <t>300,400</t>
+    <t>300,20</t>
   </si>
   <si>
     <t xml:space="preserve">样本数量，单线押分(低于此值不计入样本) </t>
@@ -191,10 +191,10 @@
     <t>连续中奖次数对应的中奖倍率，原倍率上乘以此倍率值</t>
   </si>
   <si>
-    <t>2_2|3_3|4_4|5_5</t>
-  </si>
-  <si>
-    <t>中奖次数_中奖倍率|中奖次数_中奖倍率|……</t>
+    <t>1,1_1|2_2|3_3|4_5;2,1_2|2_4|3_6|4_10</t>
+  </si>
+  <si>
+    <t>模式ID,中奖次数_中奖倍率|中奖次数_中奖倍率|……;模式ID,中奖次数_中奖倍率|中奖次数_中奖倍率|……</t>
   </si>
   <si>
     <t>免费模式下，获得目标图案奖增加免费次数</t>
@@ -212,7 +212,7 @@
     <t>最右侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1_2014004_1|2_2014005_2|3_2014006_3|4_2014007_4|5_2014008_5|6_2014009_6|7_2014010_7|8_2014011_8</t>
+    <t>1_2014004_2|2_2014005_3|3_2014006_4|4_2014007_5|5_2014008_6|6_2014009_7|7_2014010_8|8_2014011_9</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -567,17 +567,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -165,15 +165,6 @@
   </si>
   <si>
     <t>收集图案ID,触发中奖次数,获得小游戏万分比，奖励的小游戏id]</t>
-  </si>
-  <si>
-    <t>储存的平均押分：用于黄金列车、投资游戏中的奖金计算，从进X局下注中取平均值，需要区分倍场，每个倍场独立存1个</t>
-  </si>
-  <si>
-    <t>300,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">样本数量，单线押分(低于此值不计入样本) </t>
   </si>
   <si>
     <t>手动选择小游戏：中奖ID,小游戏1_小游戏2|中奖ID,小游戏1_小游戏2……</t>
@@ -1091,9 +1082,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1426,7 +1414,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="2" customWidth="1"/>
@@ -1582,7 +1570,7 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="8">
-        <v>5001003</v>
+        <v>5001007</v>
       </c>
       <c r="B7" s="9">
         <v>100100</v>
@@ -1591,12 +1579,12 @@
         <v>17</v>
       </c>
       <c r="D7" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="9" t="s">
@@ -1606,44 +1594,43 @@
       <c r="I7" s="12"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A8" s="8">
-        <v>5001007</v>
-      </c>
-      <c r="B8" s="9">
-        <v>100100</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="9">
-        <v>7</v>
+        <v>5007004</v>
+      </c>
+      <c r="B8" s="1">
+        <v>100700</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="F8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="9"/>
+      <c r="G8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A9" s="8">
-        <v>5007004</v>
+        <v>5007005</v>
       </c>
       <c r="B9" s="1">
         <v>100700</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>33</v>
@@ -1659,56 +1646,31 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A10" s="8">
-        <v>5007005</v>
+        <v>5014006</v>
       </c>
       <c r="B10" s="1">
-        <v>100700</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>32</v>
+        <v>101400</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A11" s="8">
-        <v>5014006</v>
-      </c>
-      <c r="B11" s="1">
-        <v>101400</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="6:6">
-      <c r="F12" s="15"/>
+    <row r="11" spans="6:6">
+      <c r="F11" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -1735,24 +1697,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1760,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1774,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1788,13 +1750,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1802,13 +1764,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1816,13 +1778,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1830,13 +1792,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1844,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1852,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1860,7 +1822,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1868,7 +1830,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1876,7 +1838,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1884,7 +1846,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1892,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1900,7 +1862,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1908,7 +1870,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1916,7 +1878,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1924,7 +1886,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1932,7 +1894,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1940,7 +1902,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1948,7 +1910,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1956,7 +1918,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1964,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1972,7 +1934,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1980,7 +1942,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1988,7 +1950,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1996,7 +1958,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2004,7 +1966,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2012,7 +1974,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2020,7 +1982,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2028,7 +1990,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2036,7 +1998,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2044,7 +2006,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2052,7 +2014,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2060,7 +2022,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2068,7 +2030,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2076,7 +2038,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2084,7 +2046,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2092,7 +2054,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2100,7 +2062,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2108,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2116,7 +2078,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2124,7 +2086,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2132,7 +2094,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2140,7 +2102,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2148,7 +2110,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2156,7 +2118,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -207,6 +207,18 @@
   </si>
   <si>
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
+  </si>
+  <si>
+    <t>18,20,0,10000,150,30240010</t>
+  </si>
+  <si>
+    <t>3_30240012</t>
+  </si>
+  <si>
+    <t>30240010,3,10000,30240011</t>
+  </si>
+  <si>
+    <t>1024400317,30240007_30240008|1024400417,30240007_30240009|1024400517,30240007_30240009</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -558,13 +570,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1037,7 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1079,7 +1091,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1414,7 +1425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="2" customWidth="1"/>
@@ -1471,7 +1482,7 @@
       <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="4"/>
@@ -1669,8 +1680,87 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="6:6">
-      <c r="F11" s="15"/>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A11" s="8">
+        <v>5024001</v>
+      </c>
+      <c r="B11" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A12" s="8">
+        <v>5024002</v>
+      </c>
+      <c r="B12" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A13" s="8">
+        <v>5024007</v>
+      </c>
+      <c r="B13" s="9">
+        <v>102400</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="9">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -1697,24 +1787,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1722,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1736,13 +1826,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1750,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1764,13 +1854,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1778,13 +1868,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1792,13 +1882,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1806,7 +1896,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1814,7 +1904,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1822,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1830,7 +1920,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1838,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1846,7 +1936,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1854,7 +1944,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1862,7 +1952,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1870,7 +1960,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1878,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1886,7 +1976,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1894,7 +1984,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1902,7 +1992,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1910,7 +2000,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1918,7 +2008,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1926,7 +2016,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1934,7 +2024,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1942,7 +2032,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1950,7 +2040,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1958,7 +2048,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1966,7 +2056,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1974,7 +2064,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1982,7 +2072,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1990,7 +2080,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1998,7 +2088,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2006,7 +2096,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2014,7 +2104,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2022,7 +2112,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2030,7 +2120,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2038,7 +2128,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2046,7 +2136,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2054,7 +2144,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2062,7 +2152,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2070,7 +2160,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2078,7 +2168,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2086,7 +2176,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2094,7 +2184,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2102,7 +2192,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2110,7 +2200,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2118,7 +2208,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="106">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -219,6 +219,24 @@
   </si>
   <si>
     <t>1024400317,30240007_30240008|1024400417,30240007_30240009|1024400517,30240007_30240009</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>1022400314,30220001|30220002|1022400414,30220001|30220002|1022400514,30220001|30220002</t>
+  </si>
+  <si>
+    <t>指定位置出现指定图案，且都符合，重置模式返回至目标模式</t>
+  </si>
+  <si>
+    <t>10_7|10_9,1</t>
+  </si>
+  <si>
+    <t>图案_图案位置|……|图案_图案位置，返回的目标模式ID在SpecialMode表中</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -416,12 +434,12 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -570,13 +588,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1049,11 +1067,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1070,19 +1091,19 @@
     <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1091,8 +1112,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1425,194 +1446,194 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="4" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A5" s="8">
+      <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A6" s="8">
+      <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="9"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A7" s="8">
+      <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="10">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A8" s="8">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A8" s="2">
         <v>5007004</v>
       </c>
       <c r="B8" s="1">
         <v>100700</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D8" s="1">
@@ -1621,23 +1642,23 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A9" s="8">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A9" s="2">
         <v>5007005</v>
       </c>
       <c r="B9" s="1">
         <v>100700</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="1">
@@ -1646,17 +1667,17 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A10" s="8">
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A10" s="2">
         <v>5014006</v>
       </c>
       <c r="B10" s="1">
@@ -1671,96 +1692,198 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A11" s="8">
+      <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>102400</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="10">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A12" s="8">
+      <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>102400</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="10"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A13" s="8">
+      <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>102400</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="10">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="9"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A14" s="2">
+        <v>5017004</v>
+      </c>
+      <c r="B14" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A15" s="2">
+        <v>5017005</v>
+      </c>
+      <c r="B15" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A16" s="2">
+        <v>5022007</v>
+      </c>
+      <c r="B16" s="16">
+        <v>102200</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="16">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A17" s="2">
+        <v>5022008</v>
+      </c>
+      <c r="B17" s="16">
+        <v>102200</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="16">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -1785,26 +1908,26 @@
   <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1812,13 +1935,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1826,13 +1949,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1840,13 +1963,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1854,13 +1977,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1868,13 +1991,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1882,77 +2005,77 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1960,7 +2083,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1968,7 +2091,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1976,7 +2099,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1984,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1992,7 +2115,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2000,7 +2123,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2008,7 +2131,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2016,7 +2139,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2024,7 +2147,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2032,7 +2155,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2040,7 +2163,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2048,7 +2171,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2056,7 +2179,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2064,7 +2187,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2072,7 +2195,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2080,7 +2203,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2088,7 +2211,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2096,7 +2219,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2104,7 +2227,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2112,7 +2235,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2120,7 +2243,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2128,7 +2251,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2136,7 +2259,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2144,7 +2267,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2152,7 +2275,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2160,7 +2283,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2168,7 +2291,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2176,7 +2299,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2184,7 +2307,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2192,7 +2315,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2200,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2208,7 +2331,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="109">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -227,16 +227,25 @@
     <t>雷神</t>
   </si>
   <si>
-    <t>1022400314,30220001|30220002|1022400414,30220001|30220002|1022400514,30220001|30220002</t>
+    <t>1022400314,30220001_30220002|1022400414,30220001_30220002|1022400514,30220001_30220002</t>
   </si>
   <si>
     <t>指定位置出现指定图案，且都符合，重置模式返回至目标模式</t>
   </si>
   <si>
-    <t>10_7|10_9,1</t>
+    <t>10_7|10_8</t>
   </si>
   <si>
     <t>图案_图案位置|……|图案_图案位置，返回的目标模式ID在SpecialMode表中</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>免费游戏连续中奖次数对应的中奖倍率，原倍率上乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2,1_1|2_3|3_5|4_7|5_9|6_11|7_13|8_15</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -593,12 +602,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1446,7 +1455,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1884,6 +1893,32 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="16"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A18" s="2">
+        <v>502100</v>
+      </c>
+      <c r="B18" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="16">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="16"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -1910,24 +1945,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1935,13 +1970,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1949,13 +1984,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1963,13 +1998,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1977,13 +2012,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1991,13 +2026,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2005,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2019,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2027,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2035,7 +2070,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2043,7 +2078,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2051,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2059,7 +2094,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2067,7 +2102,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2075,7 +2110,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2083,7 +2118,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2091,7 +2126,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2099,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2107,7 +2142,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2115,7 +2150,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2123,7 +2158,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2131,7 +2166,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2139,7 +2174,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2147,7 +2182,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2155,7 +2190,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2163,7 +2198,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2171,7 +2206,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2179,7 +2214,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2187,7 +2222,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2195,7 +2230,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2203,7 +2238,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2211,7 +2246,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2219,7 +2254,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2227,7 +2262,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2235,7 +2270,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2243,7 +2278,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2251,7 +2286,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2259,7 +2294,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2267,7 +2302,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2275,7 +2310,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2283,7 +2318,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2291,7 +2326,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2299,7 +2334,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2307,7 +2342,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2315,7 +2350,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2323,7 +2358,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2331,7 +2366,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="110">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -245,7 +245,10 @@
     <t>免费游戏连续中奖次数对应的中奖倍率，原倍率上乘以此倍率值</t>
   </si>
   <si>
-    <t>2,1_1|2_3|3_5|4_7|5_9|6_11|7_13|8_15</t>
+    <t>1_2</t>
+  </si>
+  <si>
+    <t>免费游戏中，连续中奖，每增加1次，中奖倍率增加2，下局游戏不会继承上局游戏的倍率</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -602,12 +605,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1914,7 +1917,7 @@
         <v>52</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
@@ -1945,24 +1948,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1970,13 +1973,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1984,13 +1987,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1998,13 +2001,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2012,13 +2015,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2026,13 +2029,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2040,13 +2043,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2054,7 +2057,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2062,7 +2065,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2070,7 +2073,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2078,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2086,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2094,7 +2097,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2102,7 +2105,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2110,7 +2113,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2118,7 +2121,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2126,7 +2129,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2134,7 +2137,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2142,7 +2145,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2150,7 +2153,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2158,7 +2161,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2166,7 +2169,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2174,7 +2177,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2182,7 +2185,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2190,7 +2193,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2198,7 +2201,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2206,7 +2209,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2214,7 +2217,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2222,7 +2225,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2230,7 +2233,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2238,7 +2241,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2246,7 +2249,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2254,7 +2257,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2262,7 +2265,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2270,7 +2273,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2278,7 +2281,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2286,7 +2289,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2294,7 +2297,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2302,7 +2305,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2310,7 +2313,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2318,7 +2321,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2326,7 +2329,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2334,7 +2337,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2342,7 +2345,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2350,7 +2353,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2358,7 +2361,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2366,7 +2369,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -600,13 +600,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1458,7 +1458,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
-        <v>502100</v>
+        <v>5021001</v>
       </c>
       <c r="B18" s="16">
         <v>102100</v>
@@ -1922,6 +1922,29 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="16"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:10">
+      <c r="A19" s="2">
+        <v>5021002</v>
+      </c>
+      <c r="B19" s="16">
+        <v>102100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="114">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t>免费游戏中，连续中奖，每增加1次，中奖倍率增加2，下局游戏不会继承上局游戏的倍率</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>免费游戏出现在2、3、4、5轴时变成百搭，并一直粘连，直至退出此模式</t>
+  </si>
+  <si>
+    <t>2,1_1|2_1|3_1|4_1|5_1|6_1|7_1|8_1|9_1|10_1</t>
+  </si>
+  <si>
+    <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -600,13 +612,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1458,7 +1470,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1945,6 +1957,31 @@
       <c r="G19" s="1" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A20" s="2">
+        <v>5018001</v>
+      </c>
+      <c r="B20" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -1971,24 +2008,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1996,13 +2033,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2010,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2024,13 +2061,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2038,13 +2075,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2052,13 +2089,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2066,13 +2103,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2080,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2088,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2096,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2104,7 +2141,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2112,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2120,7 +2157,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2128,7 +2165,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2136,7 +2173,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2144,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2152,7 +2189,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2160,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2168,7 +2205,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2176,7 +2213,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2184,7 +2221,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2192,7 +2229,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2200,7 +2237,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2208,7 +2245,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2216,7 +2253,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2224,7 +2261,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2232,7 +2269,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2240,7 +2277,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2248,7 +2285,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2256,7 +2293,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2264,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2272,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2280,7 +2317,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2288,7 +2325,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2296,7 +2333,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2304,7 +2341,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2312,7 +2349,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2320,7 +2357,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2328,7 +2365,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2336,7 +2373,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2344,7 +2381,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2352,7 +2389,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2360,7 +2397,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2368,7 +2405,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2376,7 +2413,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2384,7 +2421,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2392,7 +2429,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>2,11_10_10000|2,11_15_1000|2,11_20_100</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -617,12 +623,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1470,7 +1476,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1982,6 +1988,31 @@
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
+    </row>
+    <row r="21" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A21" s="2">
+        <v>5025001</v>
+      </c>
+      <c r="B21" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2008,24 +2039,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2033,13 +2064,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2047,13 +2078,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2061,13 +2092,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2075,13 +2106,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2089,13 +2120,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2103,13 +2134,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2117,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2125,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2133,7 +2164,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2141,7 +2172,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2149,7 +2180,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2157,7 +2188,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2165,7 +2196,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2173,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2181,7 +2212,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2189,7 +2220,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2197,7 +2228,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2205,7 +2236,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2213,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2221,7 +2252,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2229,7 +2260,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2237,7 +2268,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2245,7 +2276,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2253,7 +2284,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2261,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2269,7 +2300,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2277,7 +2308,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2285,7 +2316,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2293,7 +2324,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2301,7 +2332,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2309,7 +2340,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2317,7 +2348,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2325,7 +2356,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2333,7 +2364,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2341,7 +2372,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2349,7 +2380,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2357,7 +2388,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2365,7 +2396,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2373,7 +2404,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2381,7 +2412,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2389,7 +2420,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2397,7 +2428,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2405,7 +2436,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2413,7 +2444,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2421,7 +2452,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2429,7 +2460,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="117">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -209,7 +209,7 @@
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
   </si>
   <si>
-    <t>18,20,0,10000,150,30240010</t>
+    <t>18,20,0,10000,15,30240010</t>
   </si>
   <si>
     <t>3_30240012</t>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
+  </si>
+  <si>
+    <t>2_13_1_10000</t>
   </si>
   <si>
     <t>寒冰王座</t>
@@ -623,12 +626,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1476,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1991,13 +1994,13 @@
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
-        <v>5025001</v>
+        <v>5018002</v>
       </c>
       <c r="B21" s="16">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
@@ -2006,13 +2009,38 @@
         <v>33</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A22" s="2">
+        <v>5025001</v>
+      </c>
+      <c r="B22" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2039,24 +2067,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2064,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2078,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2092,13 +2120,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2106,13 +2134,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2120,13 +2148,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2134,13 +2162,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2148,7 +2176,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2156,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2164,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2172,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2180,7 +2208,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2188,7 +2216,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2196,7 +2224,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2204,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2212,7 +2240,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2220,7 +2248,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2228,7 +2256,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2236,7 +2264,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2244,7 +2272,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2252,7 +2280,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2260,7 +2288,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2268,7 +2296,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2276,7 +2304,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2284,7 +2312,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2292,7 +2320,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2300,7 +2328,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2308,7 +2336,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2316,7 +2344,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2324,7 +2352,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2332,7 +2360,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2340,7 +2368,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2348,7 +2376,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2356,7 +2384,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2364,7 +2392,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2372,7 +2400,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2380,7 +2408,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2388,7 +2416,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2396,7 +2424,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2404,7 +2432,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2412,7 +2440,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2420,7 +2448,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2428,7 +2456,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2436,7 +2464,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2444,7 +2472,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2452,7 +2480,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2460,7 +2488,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -82,12 +82,62 @@
         </r>
       </text>
     </comment>
+    <comment ref="G23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+中奖次数，就是触发中奖条件
+新增轴ID，就是轴内容
+中奖权重，就是根据此权重判断是否中奖，返回中奖or不中奖，如果根据轴的内容不符合中奖权重结果，则抛弃当前结果重新随机轴图案，抛弃100次后仍然不符合则使用当前结果
+中奖倍率，中奖时额外的倍率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+中奖次数，就是触发中奖条件
+新增周ID，就是轴内容
+中奖权重，就是根据此权重判断是否中奖，返回中奖or不中奖，如果根据轴的内容不符合中奖权重结果，则抛弃当前结果重新随机轴图案，抛弃100次后仍然不符合则适用当前结果
+中奖倍率，中奖时额外的倍率</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -269,7 +319,25 @@
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>2,11_10_10000|2,11_15_1000|2,11_20_100</t>
+    <t>2,11,3_10_10000|4_15_1000|5_20_100</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
+  </si>
+  <si>
+    <t>1,1_20230016_200_2|2_20230017_200_3|3_20230018_200_4|4_20230019_200_5|5_20230020_200_6|6_20230021_200_7|7_20230022_200_8|8_20230023_200_9</t>
+  </si>
+  <si>
+    <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
+  </si>
+  <si>
+    <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
+  </si>
+  <si>
+    <t>2,1_20230016_200_4|2_20230017_200_6|3_20230018_200_8|4_20230019_200_10|5_20230020_200_12|6_20230021_200_14|7_20230022_200_16|8_20230023_200_18</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1479,7 +1547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2041,6 +2109,56 @@
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A23" s="2">
+        <v>5023008</v>
+      </c>
+      <c r="B23" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A24" s="2">
+        <v>5023009</v>
+      </c>
+      <c r="B24" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2067,24 +2185,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2092,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2106,13 +2224,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2120,13 +2238,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2134,13 +2252,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2148,13 +2266,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2162,13 +2280,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2176,7 +2294,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2184,7 +2302,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2192,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2200,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2208,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2216,7 +2334,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2224,7 +2342,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2232,7 +2350,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2240,7 +2358,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2248,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2256,7 +2374,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2264,7 +2382,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2272,7 +2390,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2280,7 +2398,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2288,7 +2406,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2296,7 +2414,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2304,7 +2422,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2312,7 +2430,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2320,7 +2438,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2328,7 +2446,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2336,7 +2454,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2344,7 +2462,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2352,7 +2470,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2360,7 +2478,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2368,7 +2486,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2376,7 +2494,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2384,7 +2502,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2392,7 +2510,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2400,7 +2518,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2408,7 +2526,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2416,7 +2534,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2424,7 +2542,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2432,7 +2550,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2440,7 +2558,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2448,7 +2566,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2456,7 +2574,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2464,7 +2582,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2472,7 +2590,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2480,7 +2598,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2488,7 +2606,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -82,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0">
+    <comment ref="G24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0">
+    <comment ref="G25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="124">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -259,7 +259,7 @@
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
   </si>
   <si>
-    <t>18,20,0,10000,15,30240010</t>
+    <t>18,20,0,10000,3,30240010</t>
   </si>
   <si>
     <t>3_30240012</t>
@@ -325,10 +325,13 @@
     <t>蒸汽时代</t>
   </si>
   <si>
+    <t>2_12_1_10000</t>
+  </si>
+  <si>
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,1_20230016_200_2|2_20230017_200_3|3_20230018_200_4|4_20230019_200_5|5_20230020_200_6|6_20230021_200_7|7_20230022_200_8|8_20230023_200_9</t>
+    <t>1,1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -337,7 +340,7 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,1_20230016_200_4|2_20230017_200_6|3_20230018_200_8|4_20230019_200_10|5_20230020_200_12|6_20230021_200_14|7_20230022_200_16|8_20230023_200_18</t>
+    <t>2,1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1547,7 +1550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2111,33 +2114,29 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A23" s="2">
-        <v>5023008</v>
-      </c>
-      <c r="B23" s="16">
-        <v>102300</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="16"/>
       <c r="C23" t="s">
         <v>61</v>
       </c>
       <c r="D23" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>63</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
-        <v>5023009</v>
+        <v>5023008</v>
       </c>
       <c r="B24" s="16">
         <v>102300</v>
@@ -2146,19 +2145,44 @@
         <v>61</v>
       </c>
       <c r="D24" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A25" s="2">
+        <v>5023009</v>
+      </c>
+      <c r="B25" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2185,24 +2209,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
         <v>70</v>
       </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2210,13 +2234,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2224,13 +2248,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2238,13 +2262,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2252,13 +2276,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2266,13 +2290,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2280,13 +2304,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2294,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2302,7 +2326,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2310,7 +2334,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2318,7 +2342,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2326,7 +2350,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2334,7 +2358,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2342,7 +2366,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2350,7 +2374,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2358,7 +2382,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2366,7 +2390,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2374,7 +2398,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2382,7 +2406,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2390,7 +2414,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2398,7 +2422,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2406,7 +2430,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2414,7 +2438,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2422,7 +2446,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2430,7 +2454,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2438,7 +2462,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2446,7 +2470,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2454,7 +2478,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2462,7 +2486,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2470,7 +2494,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2478,7 +2502,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2486,7 +2510,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2494,7 +2518,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2502,7 +2526,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2510,7 +2534,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2518,7 +2542,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2526,7 +2550,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2534,7 +2558,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2542,7 +2566,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2550,7 +2574,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2558,7 +2582,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2566,7 +2590,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2574,7 +2598,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2582,7 +2606,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2590,7 +2614,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2598,7 +2622,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2606,7 +2630,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -2114,8 +2114,12 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A23" s="2"/>
-      <c r="B23" s="16"/>
+      <c r="A23" s="2">
+        <v>5023005</v>
+      </c>
+      <c r="B23" s="16">
+        <v>102300</v>
+      </c>
       <c r="C23" t="s">
         <v>61</v>
       </c>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -82,12 +82,62 @@
         </r>
       </text>
     </comment>
+    <comment ref="G23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+中奖次数，就是触发中奖条件
+新增轴ID，就是轴内容
+中奖权重，就是根据此权重判断是否中奖，返回中奖or不中奖，如果根据轴的内容不符合中奖权重结果，则抛弃当前结果重新随机轴图案，抛弃100次后仍然不符合则使用当前结果
+中奖倍率，中奖时额外的倍率</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+中奖次数，就是触发中奖条件
+新增周ID，就是轴内容
+中奖权重，就是根据此权重判断是否中奖，返回中奖or不中奖，如果根据轴的内容不符合中奖权重结果，则抛弃当前结果重新随机轴图案，抛弃100次后仍然不符合则适用当前结果
+中奖倍率，中奖时额外的倍率</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -209,7 +259,7 @@
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
   </si>
   <si>
-    <t>18,20,0,10000,150,30240010</t>
+    <t>18,20,0,10000,3,30240010</t>
   </si>
   <si>
     <t>3_30240012</t>
@@ -263,10 +313,31 @@
     <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
   </si>
   <si>
+    <t>2_13_1_10000</t>
+  </si>
+  <si>
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>2,11_10_10000|2,11_15_1000|2,11_20_100</t>
+    <t>2,11,3_10_10000|4_15_1000|5_20_100</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
+  </si>
+  <si>
+    <t>1,1_20230016_200_2|2_20230017_200_3|3_20230018_200_4|4_20230019_200_5|5_20230020_200_6|6_20230021_200_7|7_20230022_200_8|8_20230023_200_9</t>
+  </si>
+  <si>
+    <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
+  </si>
+  <si>
+    <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
+  </si>
+  <si>
+    <t>2,1_20230016_200_4|2_20230017_200_6|3_20230018_200_8|4_20230019_200_10|5_20230020_200_12|6_20230021_200_14|7_20230022_200_16|8_20230023_200_18</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -618,12 +689,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1476,7 +1547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -1991,13 +2062,13 @@
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
-        <v>5025001</v>
+        <v>5018002</v>
       </c>
       <c r="B21" s="16">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
@@ -2006,13 +2077,88 @@
         <v>33</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
+    </row>
+    <row r="22" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A22" s="2">
+        <v>5025001</v>
+      </c>
+      <c r="B22" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A23" s="2">
+        <v>5023008</v>
+      </c>
+      <c r="B23" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A24" s="2">
+        <v>5023009</v>
+      </c>
+      <c r="B24" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2039,24 +2185,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2064,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2078,13 +2224,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2092,13 +2238,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2106,13 +2252,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2120,13 +2266,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2134,13 +2280,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2148,7 +2294,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2156,7 +2302,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2164,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2172,7 +2318,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2180,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2188,7 +2334,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2196,7 +2342,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2204,7 +2350,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2212,7 +2358,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2220,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2228,7 +2374,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2236,7 +2382,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2244,7 +2390,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2252,7 +2398,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2260,7 +2406,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2268,7 +2414,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2276,7 +2422,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2284,7 +2430,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2292,7 +2438,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2300,7 +2446,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2308,7 +2454,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2316,7 +2462,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2324,7 +2470,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2332,7 +2478,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2340,7 +2486,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2348,7 +2494,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2356,7 +2502,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2364,7 +2510,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2372,7 +2518,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2380,7 +2526,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2388,7 +2534,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2396,7 +2542,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2404,7 +2550,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2412,7 +2558,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2420,7 +2566,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2428,7 +2574,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2436,7 +2582,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2444,7 +2590,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2452,7 +2598,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2460,7 +2606,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -82,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0">
+    <comment ref="G24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0">
+    <comment ref="G25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="124">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -325,10 +325,13 @@
     <t>蒸汽时代</t>
   </si>
   <si>
+    <t>2_12_1_10000</t>
+  </si>
+  <si>
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,1_20230016_200_2|2_20230017_200_3|3_20230018_200_4|4_20230019_200_5|5_20230020_200_6|6_20230021_200_7|7_20230022_200_8|8_20230023_200_9</t>
+    <t>1,1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -337,7 +340,7 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,1_20230016_200_4|2_20230017_200_6|3_20230018_200_8|4_20230019_200_10|5_20230020_200_12|6_20230021_200_14|7_20230022_200_16|8_20230023_200_18</t>
+    <t>2,1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -689,17 +692,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1547,7 +1550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2112,7 +2115,7 @@
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
-        <v>5023008</v>
+        <v>5023005</v>
       </c>
       <c r="B23" s="16">
         <v>102300</v>
@@ -2121,23 +2124,23 @@
         <v>61</v>
       </c>
       <c r="D23" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>63</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
-        <v>5023009</v>
+        <v>5023008</v>
       </c>
       <c r="B24" s="16">
         <v>102300</v>
@@ -2146,19 +2149,44 @@
         <v>61</v>
       </c>
       <c r="D24" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
+    </row>
+    <row r="25" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A25" s="2">
+        <v>5023009</v>
+      </c>
+      <c r="B25" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2185,24 +2213,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" t="s">
         <v>70</v>
       </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2210,13 +2238,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2224,13 +2252,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2238,13 +2266,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2252,13 +2280,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2266,13 +2294,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2280,13 +2308,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2294,7 +2322,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2302,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2310,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2318,7 +2346,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2326,7 +2354,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2334,7 +2362,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2342,7 +2370,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2350,7 +2378,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2358,7 +2386,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2366,7 +2394,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2374,7 +2402,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2382,7 +2410,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2390,7 +2418,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2398,7 +2426,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2406,7 +2434,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2414,7 +2442,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2422,7 +2450,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2430,7 +2458,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2438,7 +2466,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2446,7 +2474,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2454,7 +2482,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2462,7 +2490,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2470,7 +2498,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2478,7 +2506,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2486,7 +2514,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2494,7 +2522,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2502,7 +2530,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2510,7 +2538,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2518,7 +2546,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2526,7 +2554,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2534,7 +2562,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2542,7 +2570,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2550,7 +2578,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2558,7 +2586,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2566,7 +2594,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2574,7 +2602,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2582,7 +2610,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2590,7 +2618,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2598,7 +2626,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2606,7 +2634,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -331,7 +331,7 @@
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
+    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -340,7 +340,31 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18</t>
+    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福马模式特效</t>
+  </si>
+  <si>
+    <t>1,1000</t>
+  </si>
+  <si>
+    <t>模式，概率假进福马模式万分比</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金钱兔模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1550,7 +1574,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2187,6 +2211,81 @@
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A26" s="2">
+        <v>5034001</v>
+      </c>
+      <c r="B26" s="16">
+        <v>103400</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A27" s="2">
+        <v>5035001</v>
+      </c>
+      <c r="B27" s="16">
+        <v>103500</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A28" s="2">
+        <v>5035011</v>
+      </c>
+      <c r="B28" s="16">
+        <v>103501</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2213,24 +2312,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2238,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2252,13 +2351,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2266,13 +2365,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2280,13 +2379,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2294,13 +2393,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2308,13 +2407,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2322,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2330,7 +2429,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2338,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2346,7 +2445,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2354,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2362,7 +2461,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2370,7 +2469,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2378,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2386,7 +2485,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2394,7 +2493,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2402,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2410,7 +2509,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2418,7 +2517,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2426,7 +2525,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2434,7 +2533,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2442,7 +2541,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2450,7 +2549,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2458,7 +2557,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2466,7 +2565,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2474,7 +2573,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2482,7 +2581,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2490,7 +2589,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2498,7 +2597,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2506,7 +2605,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2514,7 +2613,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2522,7 +2621,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2530,7 +2629,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2538,7 +2637,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2546,7 +2645,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2554,7 +2653,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2562,7 +2661,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2570,7 +2669,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2578,7 +2677,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2586,7 +2685,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2594,7 +2693,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2602,7 +2701,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2610,7 +2709,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2618,7 +2717,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2626,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2634,7 +2733,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -341,6 +341,30 @@
   </si>
   <si>
     <t>2,1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18</t>
+  </si>
+  <si>
+    <t>神马飞扬</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福马模式特效</t>
+  </si>
+  <si>
+    <t>1,1000</t>
+  </si>
+  <si>
+    <t>模式，概率假进福马模式万分比</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金钱兔模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1550,7 +1574,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2187,6 +2211,81 @@
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
+    </row>
+    <row r="26" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A26" s="2">
+        <v>5034001</v>
+      </c>
+      <c r="B26" s="16">
+        <v>103400</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A27" s="2">
+        <v>5035001</v>
+      </c>
+      <c r="B27" s="16">
+        <v>103500</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A28" s="2">
+        <v>5035011</v>
+      </c>
+      <c r="B28" s="16">
+        <v>103501</v>
+      </c>
+      <c r="C28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2213,24 +2312,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2238,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2252,13 +2351,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2266,13 +2365,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2280,13 +2379,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2294,13 +2393,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2308,13 +2407,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2322,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2330,7 +2429,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2338,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2346,7 +2445,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2354,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2362,7 +2461,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2370,7 +2469,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2378,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2386,7 +2485,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2394,7 +2493,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2402,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2410,7 +2509,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2418,7 +2517,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2426,7 +2525,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2434,7 +2533,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2442,7 +2541,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2450,7 +2549,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2458,7 +2557,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2466,7 +2565,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2474,7 +2573,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2482,7 +2581,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2490,7 +2589,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2498,7 +2597,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2506,7 +2605,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2514,7 +2613,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2522,7 +2621,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2530,7 +2629,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2538,7 +2637,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2546,7 +2645,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2554,7 +2653,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2562,7 +2661,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2570,7 +2669,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2578,7 +2677,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2586,7 +2685,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2594,7 +2693,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2602,7 +2701,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2610,7 +2709,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2618,7 +2717,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2626,7 +2725,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2634,7 +2733,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -331,7 +331,7 @@
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
+    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -340,7 +340,7 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18</t>
+    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42|21_20230022_50_44|22_20230023_0_46|23_20230022_50_48|24_20230023_0_50|25_20230022_50_52|26_20230023_0_54|27_20230022_50_56|28_20230023_0_58|29_20230022_50_60|30_20230023_0_62</t>
   </si>
   <si>
     <t>神马飞扬</t>
@@ -716,17 +716,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2203,7 +2203,7 @@
       <c r="E25" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" t="s">
         <v>67</v>
       </c>
       <c r="G25" s="1" t="s">

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -307,7 +307,7 @@
     <t>免费游戏出现在2、3、4、5轴时变成百搭，并一直粘连，直至退出此模式</t>
   </si>
   <si>
-    <t>2,1_1|2_1|3_1|4_1|5_1|6_1|7_1|8_1|9_1|10_1</t>
+    <t>2,1_30|2_20|3_20|4_10|5_10|6_3|7_3|8_2|9_1|10_1</t>
   </si>
   <si>
     <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
@@ -716,17 +716,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -307,7 +307,7 @@
     <t>免费游戏出现在2、3、4、5轴时变成百搭，并一直粘连，直至退出此模式</t>
   </si>
   <si>
-    <t>2,1_30|2_20|3_20|4_10|5_10|6_3|7_3|8_2|9_1|10_1</t>
+    <t>2,1_0|2_0|3_0|4_0|5_0|6_0|7_15|8_25|9_30|10_30</t>
   </si>
   <si>
     <t>模式，图案ID_权重|图案ID_权重|图案ID_权重|……</t>
@@ -721,12 +721,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -331,7 +331,7 @@
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
+    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9|9_20230022_50_10|10_20230023_0_11|11_20230022_50_12|12_20230023_0_13|13_20230022_50_14|14_20230023_0_15|15_20230022_50_16|16_20230023_0_17|17_20230022_50_18|18_20230023_0_19</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -340,7 +340,7 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42|21_20230022_50_44|22_20230023_0_46|23_20230022_50_48|24_20230023_0_50|25_20230022_50_52|26_20230023_0_54|27_20230022_50_56|28_20230023_0_58|29_20230022_50_60|30_20230023_0_62</t>
+    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42|21_20230022_50_44|22_20230023_0_46|23_20230022_50_48|24_20230023_0_50|25_20230022_50_52|26_20230023_0_54|27_20230022_50_56|28_20230023_0_58|29_20230022_50_60|30_20230023_0_62|31_20230022_50_64|31_20230023_0_66|33_20230022_50_68|34_20230023_0_70|35_20230022_50_72|36_20230023_0_74|37_20230022_50_76|38_20230023_0_78|39_20230022_50_80|40_20230023_0_82|41_20230022_50_84|42_20230023_0_86|43_20230022_50_88|44_20230023_0_90|45_20230022_50_92|46_20230023_0_94|47_20230022_50_96|48_20230023_0_98|49_20230022_50_100|50_20230023_0_102|51_20230022_50_104|52_20230023_0_106|53_20230022_50_108|54_20230023_0_110|55_20230022_50_112|56_20230023_0_114|57_20230022_50_116|58_20230023_0_118|59_20230022_50_120|60_20230023_0_122|61_20230022_50_124|62_20230023_0_126|62_20230022_50_128|64_20230023_0_130|65_20230022_50_132|66_20230023_0_134|67_20230022_50_136|68_20230023_0_138|69_20230023_0_140|70_20230022_50_142|71_20230023_0_144|72_20230022_50_146|73_20230023_0_148|74_20230022_50_150|75_20230023_0_152|51_20230022_50_154|52_20230023_0_156|53_20230022_50_158|54_20230023_0_160|55_20230022_50_162|56_20230023_0_164|57_20230022_50_166|58_20230023_0_168|59_20230022_50_170|60_20230023_0_172|76_20230022_50_174|77_20230023_0_176|78_20230022_50_178|79_20230023_0_180|80_20230022_50_192|81_20230023_0_194|82_20230022_50_196|83_20230023_0_198</t>
   </si>
   <si>
     <t>神马飞扬</t>
@@ -716,12 +716,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="133">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -283,7 +283,7 @@
     <t>指定位置出现指定图案，且都符合，重置模式返回至目标模式</t>
   </si>
   <si>
-    <t>10_7|10_8</t>
+    <t>9_7|9_8</t>
   </si>
   <si>
     <t>图案_图案位置|……|图案_图案位置，返回的目标模式ID在SpecialMode表中</t>
@@ -301,6 +301,9 @@
     <t>免费游戏中，连续中奖，每增加1次，中奖倍率增加2，下局游戏不会继承上局游戏的倍率</t>
   </si>
   <si>
+    <t>2_12_10_10000</t>
+  </si>
+  <si>
     <t>篮球巨星</t>
   </si>
   <si>
@@ -331,7 +334,7 @@
     <t>常规模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9</t>
+    <t>1,0_20230016_5000_1|1_20230016_5000_2|2_20230017_4000_3|3_20230018_1000_4|4_20230019_500_5|5_20230020_300_6|6_20230021_100_7|7_20230022_50_8|8_20230023_0_9|9_20230022_50_10|10_20230023_0_11|11_20230022_50_12|12_20230023_0_13|13_20230022_50_14|14_20230023_0_15|15_20230022_50_16|16_20230023_0_17|17_20230022_50_18|18_20230023_0_19</t>
   </si>
   <si>
     <t>中奖次数_新增的轴ID_此次中奖权重_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
@@ -340,7 +343,7 @@
     <t>免费模式下，最左侧列有中奖图案时，新增一列进行摇奖</t>
   </si>
   <si>
-    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42|21_20230022_50_44|22_20230023_0_46|23_20230022_50_48|24_20230023_0_50|25_20230022_50_52|26_20230023_0_54|27_20230022_50_56|28_20230023_0_58|29_20230022_50_60|30_20230023_0_62</t>
+    <t>2,0_20230016_5000_2|1_20230016_5000_4|2_20230017_4000_6|3_20230018_1000_8|4_20230019_500_10|5_20230020_300_12|6_20230021_100_14|7_20230022_50_16|8_20230023_0_18|9_20230022_50_20|10_20230023_0_22|11_20230022_50_24|12_20230023_0_26|13_20230022_50_28|14_20230023_0_30|15_20230022_50_32|16_20230023_0_34|17_20230022_50_36|18_20230023_0_38|19_20230022_50_40|20_20230023_0_42|21_20230022_50_44|22_20230023_0_46|23_20230022_50_48|24_20230023_0_50|25_20230022_50_52|26_20230023_0_54|27_20230022_50_56|28_20230023_0_58|29_20230022_50_60|30_20230023_0_62|31_20230022_50_64|31_20230023_0_66|33_20230022_50_68|34_20230023_0_70|35_20230022_50_72|36_20230023_0_74|37_20230022_50_76|38_20230023_0_78|39_20230022_50_80|40_20230023_0_82|41_20230022_50_84|42_20230023_0_86|43_20230022_50_88|44_20230023_0_90|45_20230022_50_92|46_20230023_0_94|47_20230022_50_96|48_20230023_0_98|49_20230022_50_100|50_20230023_0_102|51_20230022_50_104|52_20230023_0_106|53_20230022_50_108|54_20230023_0_110|55_20230022_50_112|56_20230023_0_114|57_20230022_50_116|58_20230023_0_118|59_20230022_50_120|60_20230023_0_122|61_20230022_50_124|62_20230023_0_126|62_20230022_50_128|64_20230023_0_130|65_20230022_50_132|66_20230023_0_134|67_20230022_50_136|68_20230023_0_138|69_20230023_0_140|70_20230022_50_142|71_20230023_0_144|72_20230022_50_146|73_20230023_0_148|74_20230022_50_150|75_20230023_0_152|51_20230022_50_154|52_20230023_0_156|53_20230022_50_158|54_20230023_0_160|55_20230022_50_162|56_20230023_0_164|57_20230022_50_166|58_20230023_0_168|59_20230022_50_170|60_20230023_0_172|76_20230022_50_174|77_20230023_0_176|78_20230022_50_178|79_20230023_0_180|80_20230022_50_192|81_20230023_0_194|82_20230022_50_196|83_20230023_0_198</t>
   </si>
   <si>
     <t>神马飞扬</t>
@@ -721,12 +724,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2056,7 +2059,7 @@
         <v>33</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>35</v>
@@ -2070,19 +2073,19 @@
         <v>101800</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -2095,7 +2098,7 @@
         <v>101800</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
@@ -2104,7 +2107,7 @@
         <v>33</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
@@ -2120,7 +2123,7 @@
         <v>102500</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1">
         <v>5</v>
@@ -2129,7 +2132,7 @@
         <v>33</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
@@ -2145,7 +2148,7 @@
         <v>102300</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1">
         <v>5</v>
@@ -2154,7 +2157,7 @@
         <v>33</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
@@ -2170,19 +2173,19 @@
         <v>102300</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="1">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -2195,19 +2198,19 @@
         <v>102300</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1">
         <v>9</v>
       </c>
       <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -2220,19 +2223,19 @@
         <v>103400</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -2245,19 +2248,19 @@
         <v>103500</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -2270,19 +2273,19 @@
         <v>103501</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -2312,24 +2315,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2337,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2351,13 +2354,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2365,13 +2368,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2379,13 +2382,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2393,13 +2396,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2407,13 +2410,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2421,7 +2424,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2429,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2437,7 +2440,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2445,7 +2448,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2453,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2461,7 +2464,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2469,7 +2472,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2477,7 +2480,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2485,7 +2488,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2493,7 +2496,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2501,7 +2504,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2509,7 +2512,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2517,7 +2520,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2525,7 +2528,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2533,7 +2536,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2541,7 +2544,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2549,7 +2552,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2557,7 +2560,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2565,7 +2568,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2573,7 +2576,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2581,7 +2584,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2589,7 +2592,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2597,7 +2600,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2605,7 +2608,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2613,7 +2616,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2621,7 +2624,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2629,7 +2632,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2637,7 +2640,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2645,7 +2648,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2653,7 +2656,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2661,7 +2664,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2669,7 +2672,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2677,7 +2680,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2685,7 +2688,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2693,7 +2696,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2701,7 +2704,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2709,7 +2712,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2717,7 +2720,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2725,7 +2728,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2733,7 +2736,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -368,6 +368,24 @@
   </si>
   <si>
     <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福鼠模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进福鼠模式万分比</t>
+  </si>
+  <si>
+    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
+  </si>
+  <si>
+    <t>2,0_1</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -719,17 +737,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1577,7 +1595,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2289,6 +2307,56 @@
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
+    </row>
+    <row r="29" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A29" s="2">
+        <v>5036001</v>
+      </c>
+      <c r="B29" s="16">
+        <v>103600</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A30" s="2">
+        <v>5036002</v>
+      </c>
+      <c r="B30" s="16">
+        <v>103600</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2315,24 +2383,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2340,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2354,13 +2422,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2368,13 +2436,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2382,13 +2450,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2396,13 +2464,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2410,13 +2478,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2424,7 +2492,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2432,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2440,7 +2508,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2448,7 +2516,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2456,7 +2524,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2464,7 +2532,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2472,7 +2540,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2480,7 +2548,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2488,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2496,7 +2564,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2504,7 +2572,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2512,7 +2580,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2520,7 +2588,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2528,7 +2596,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2536,7 +2604,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2544,7 +2612,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2552,7 +2620,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2560,7 +2628,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2568,7 +2636,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2576,7 +2644,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2584,7 +2652,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2592,7 +2660,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2600,7 +2668,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2608,7 +2676,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2616,7 +2684,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2624,7 +2692,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2632,7 +2700,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2640,7 +2708,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2648,7 +2716,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2656,7 +2724,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2664,7 +2732,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2672,7 +2740,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2680,7 +2748,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2688,7 +2756,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2696,7 +2764,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2704,7 +2772,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2712,7 +2780,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2720,7 +2788,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2728,7 +2796,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2736,7 +2804,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="148">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -356,6 +356,33 @@
   </si>
   <si>
     <t>模式，概率假进福马模式万分比</t>
+  </si>
+  <si>
+    <t>随机图标</t>
+  </si>
+  <si>
+    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+  </si>
+  <si>
+    <t>随机图标_随机图标概率</t>
+  </si>
+  <si>
+    <t>随机到图标得概率（万分比）</t>
+  </si>
+  <si>
+    <t>6_5000_2000</t>
+  </si>
+  <si>
+    <t>转轴上最低出现元素个数_随机到图标得概率（万分比）_随机图标变成wild概率</t>
+  </si>
+  <si>
+    <t>元素滚轴</t>
+  </si>
+  <si>
+    <t>1_2034002;2_2034003;3_2034004;4_2034005;5_2034006;6_2034007</t>
+  </si>
+  <si>
+    <t>元素id_元素滚轴</t>
   </si>
   <si>
     <t>金蛇招财</t>
@@ -737,17 +764,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1595,7 +1622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2260,22 +2287,22 @@
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
-        <v>5035001</v>
+        <v>5034002</v>
       </c>
       <c r="B27" s="16">
-        <v>103500</v>
+        <v>103400</v>
       </c>
       <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
@@ -2285,78 +2312,153 @@
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
-        <v>5035011</v>
+        <v>5034003</v>
       </c>
       <c r="B28" s="16">
-        <v>103501</v>
+        <v>103400</v>
       </c>
       <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="14" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
-        <v>5036001</v>
+        <v>5034004</v>
       </c>
       <c r="B29" s="16">
-        <v>103600</v>
+        <v>103400</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
-        <v>5036002</v>
+        <v>5035001</v>
       </c>
       <c r="B30" s="16">
-        <v>103600</v>
+        <v>103500</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
+    </row>
+    <row r="31" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A31" s="2">
+        <v>5035011</v>
+      </c>
+      <c r="B31" s="16">
+        <v>103501</v>
+      </c>
+      <c r="C31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A32" s="2">
+        <v>5036001</v>
+      </c>
+      <c r="B32" s="16">
+        <v>103600</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A33" s="2">
+        <v>5036002</v>
+      </c>
+      <c r="B33" s="16">
+        <v>103600</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2383,24 +2485,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2408,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2422,13 +2524,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2436,13 +2538,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2450,13 +2552,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2464,13 +2566,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2478,13 +2580,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2492,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2500,7 +2602,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2508,7 +2610,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2516,7 +2618,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2524,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2532,7 +2634,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2540,7 +2642,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2548,7 +2650,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2556,7 +2658,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2564,7 +2666,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2572,7 +2674,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2580,7 +2682,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2588,7 +2690,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2596,7 +2698,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2604,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2612,7 +2714,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2620,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2628,7 +2730,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2636,7 +2738,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2644,7 +2746,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2652,7 +2754,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2660,7 +2762,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2668,7 +2770,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2676,7 +2778,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2684,7 +2786,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2692,7 +2794,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2700,7 +2802,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2708,7 +2810,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2716,7 +2818,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2724,7 +2826,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2732,7 +2834,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2740,7 +2842,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2748,7 +2850,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2756,7 +2858,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2764,7 +2866,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2772,7 +2874,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2780,7 +2882,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2788,7 +2890,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2796,7 +2898,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2804,7 +2906,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="154">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -413,6 +413,24 @@
   </si>
   <si>
     <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_1000|6_20_100</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1622,7 +1640,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
@@ -2459,6 +2477,156 @@
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A34" s="2">
+        <v>5028001</v>
+      </c>
+      <c r="B34" s="16">
+        <v>102800</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A35" s="2">
+        <v>5028002</v>
+      </c>
+      <c r="B35" s="16">
+        <v>102800</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A36" s="2">
+        <v>5034011</v>
+      </c>
+      <c r="B36" s="16">
+        <v>103401</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A37" s="2">
+        <v>5034012</v>
+      </c>
+      <c r="B37" s="16">
+        <v>103402</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A38" s="2">
+        <v>5034013</v>
+      </c>
+      <c r="B38" s="16">
+        <v>103403</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A39" s="2">
+        <v>5034014</v>
+      </c>
+      <c r="B39" s="16">
+        <v>103404</v>
+      </c>
+      <c r="C39" t="s">
+        <v>97</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2485,24 +2653,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2510,13 +2678,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2524,13 +2692,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2538,13 +2706,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2552,13 +2720,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2566,13 +2734,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2580,13 +2748,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2594,7 +2762,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2602,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2610,7 +2778,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2618,7 +2786,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2626,7 +2794,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2634,7 +2802,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2642,7 +2810,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2650,7 +2818,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2658,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2666,7 +2834,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2674,7 +2842,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2682,7 +2850,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2690,7 +2858,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2698,7 +2866,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2706,7 +2874,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2714,7 +2882,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2722,7 +2890,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2730,7 +2898,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2738,7 +2906,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2746,7 +2914,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2754,7 +2922,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2762,7 +2930,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2770,7 +2938,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2778,7 +2946,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2786,7 +2954,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2794,7 +2962,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2802,7 +2970,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2810,7 +2978,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2818,7 +2986,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2826,7 +2994,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2834,7 +3002,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2842,7 +3010,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2850,7 +3018,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2858,7 +3026,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2866,7 +3034,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2874,7 +3042,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2882,7 +3050,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2890,7 +3058,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2898,7 +3066,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2906,7 +3074,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="156">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -431,6 +431,12 @@
   </si>
   <si>
     <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400326,30200009_30200014</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -787,18 +793,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -807,6 +813,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1004,12 +1016,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1134,7 +1161,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1146,122 +1173,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1269,20 +1296,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1297,17 +1327,29 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1364,11 +1406,18 @@
     <cellStyle name="常规 80" xfId="50"/>
     <cellStyle name="常规 2" xfId="51"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1640,185 +1689,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <v>100100</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="10"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>100100</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>100100</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="10"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2">
@@ -1836,14 +1885,14 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="2">
@@ -1861,14 +1910,14 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -1886,96 +1935,96 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>102400</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>102400</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="10"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>102400</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="10"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="2">
@@ -1993,14 +2042,14 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -2018,98 +2067,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>5022007</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <v>102200</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="16"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="2">
         <v>5022008</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>102200</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="16"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
         <v>5021001</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <v>102100</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="2">
         <v>5021002</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="17">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2121,7 +2170,7 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2132,7 +2181,7 @@
       <c r="A20" s="2">
         <v>5018001</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2144,20 +2193,20 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
         <v>5018002</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2169,20 +2218,20 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="2">
         <v>5025001</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2194,20 +2243,20 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
         <v>5023005</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="17">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2219,20 +2268,20 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
         <v>5023008</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2244,20 +2293,20 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="15" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="2">
         <v>5023009</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2275,14 +2324,14 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="2">
         <v>5034001</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2294,20 +2343,20 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
         <v>5034002</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2319,20 +2368,20 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="15" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
         <v>5034003</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2344,20 +2393,20 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
         <v>5034004</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2369,20 +2418,20 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
         <v>5035001</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2394,20 +2443,20 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="2">
         <v>5035011</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
@@ -2419,20 +2468,20 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="2">
         <v>5036001</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
@@ -2444,20 +2493,20 @@
       <c r="E32" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="2">
         <v>5036002</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
@@ -2469,20 +2518,20 @@
       <c r="E33" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="15" t="s">
         <v>90</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:10">
       <c r="A34" s="2">
         <v>5028001</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <v>102800</v>
       </c>
       <c r="C34" t="s">
@@ -2494,20 +2543,20 @@
       <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="15" t="s">
         <v>93</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-    </row>
-    <row r="35" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:10">
       <c r="A35" s="2">
         <v>5028002</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="17">
         <v>102800</v>
       </c>
       <c r="C35" t="s">
@@ -2519,20 +2568,20 @@
       <c r="E35" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="15" t="s">
         <v>95</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:10">
       <c r="A36" s="2">
         <v>5034011</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="17">
         <v>103401</v>
       </c>
       <c r="C36" t="s">
@@ -2544,20 +2593,20 @@
       <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-    </row>
-    <row r="37" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:10">
       <c r="A37" s="2">
         <v>5034012</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <v>103402</v>
       </c>
       <c r="C37" t="s">
@@ -2569,20 +2618,20 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="15" t="s">
         <v>74</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:10">
       <c r="A38" s="2">
         <v>5034013</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="17">
         <v>103403</v>
       </c>
       <c r="C38" t="s">
@@ -2594,20 +2643,20 @@
       <c r="E38" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:10">
       <c r="A39" s="2">
         <v>5034014</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="17">
         <v>103404</v>
       </c>
       <c r="C39" t="s">
@@ -2619,23 +2668,55 @@
       <c r="E39" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A40" s="3">
+        <v>5020001</v>
+      </c>
+      <c r="B40" s="18">
+        <v>102000</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="18">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="18"/>
+    </row>
+    <row r="44" ht="16.5" spans="1:10">
+      <c r="E44" s="21"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E44">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2653,24 +2734,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2678,13 +2759,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2692,13 +2773,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2706,13 +2787,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2720,13 +2801,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2734,13 +2815,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2748,13 +2829,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2762,7 +2843,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2770,7 +2851,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2778,7 +2859,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2786,7 +2867,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2794,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2802,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2810,7 +2891,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2818,7 +2899,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2826,7 +2907,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2834,7 +2915,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2842,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2850,7 +2931,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2858,7 +2939,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2866,7 +2947,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2874,7 +2955,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2882,7 +2963,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2890,7 +2971,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2898,7 +2979,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2906,7 +2987,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2914,7 +2995,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2922,7 +3003,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2930,7 +3011,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2938,7 +3019,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2946,7 +3027,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2954,7 +3035,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2962,7 +3043,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2970,7 +3051,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2978,7 +3059,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2986,7 +3067,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2994,7 +3075,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3002,7 +3083,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3010,7 +3091,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3018,7 +3099,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3026,7 +3107,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3034,7 +3115,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3042,7 +3123,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3050,7 +3131,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3058,7 +3139,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3066,7 +3147,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3074,7 +3155,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -436,7 +436,7 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>1020400326,30200009_30200014</t>
+    <t>1020400334,30200009_30200014</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -793,12 +793,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -370,7 +370,7 @@
     <t>随机到图标得概率（万分比）</t>
   </si>
   <si>
-    <t>6_5000_2000</t>
+    <t>5_3000_2000</t>
   </si>
   <si>
     <t>转轴上最低出现元素个数_随机到图标得概率（万分比）_随机图标变成wild概率</t>
@@ -769,12 +769,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="149">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -259,7 +259,7 @@
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
   </si>
   <si>
-    <t>18,20,0,10000,3,30240010</t>
+    <t>18,20,0,10000,150,30240010</t>
   </si>
   <si>
     <t>3_30240012</t>
@@ -361,7 +361,7 @@
     <t>随机图标</t>
   </si>
   <si>
-    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+    <t>1_0;2_10;3_30;4_30;5_30;6_0</t>
   </si>
   <si>
     <t>随机图标_随机图标概率</t>
@@ -370,7 +370,7 @@
     <t>随机到图标得概率（万分比）</t>
   </si>
   <si>
-    <t>5_3000_2000</t>
+    <t>5_3000_1000</t>
   </si>
   <si>
     <t>转轴上最低出现元素个数_随机到图标得概率（万分比）_随机图标变成wild概率</t>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>常规模式下，概率触发金钱兔模式特效</t>
+  </si>
+  <si>
+    <t>1,500</t>
   </si>
   <si>
     <t>模式，概率假进金钱兔模式万分比</t>
@@ -764,12 +767,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2377,10 +2380,10 @@
         <v>83</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -2393,7 +2396,7 @@
         <v>103501</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -2402,10 +2405,10 @@
         <v>83</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -2418,19 +2421,19 @@
         <v>103600</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2443,19 +2446,19 @@
         <v>103600</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -2485,24 +2488,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
         <v>95</v>
       </c>
-      <c r="D2" t="s">
-        <v>94</v>
-      </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2510,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2524,13 +2527,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2538,13 +2541,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2552,13 +2555,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2566,13 +2569,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2580,13 +2583,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2594,7 +2597,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2602,7 +2605,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2610,7 +2613,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2618,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2626,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2634,7 +2637,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2642,7 +2645,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2650,7 +2653,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2658,7 +2661,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2666,7 +2669,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2674,7 +2677,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2682,7 +2685,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2690,7 +2693,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2698,7 +2701,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2706,7 +2709,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2714,7 +2717,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2722,7 +2725,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2730,7 +2733,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2738,7 +2741,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2746,7 +2749,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2754,7 +2757,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2762,7 +2765,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2770,7 +2773,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2778,7 +2781,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2786,7 +2789,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2794,7 +2797,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2802,7 +2805,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2810,7 +2813,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2818,7 +2821,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2826,7 +2829,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2834,7 +2837,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2842,7 +2845,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2850,7 +2853,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2858,7 +2861,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2866,7 +2869,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2874,7 +2877,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2882,7 +2885,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2890,7 +2893,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2898,7 +2901,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2906,7 +2909,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="160">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -259,7 +259,7 @@
     <t>中奖次数_新增的轴ID_中奖倍率|中奖次数_新增的轴ID_中奖倍率|……</t>
   </si>
   <si>
-    <t>18,20,0,10000,3,30240010</t>
+    <t>18,20,0,10000,150,30240010</t>
   </si>
   <si>
     <t>3_30240012</t>
@@ -361,58 +361,94 @@
     <t>随机图标</t>
   </si>
   <si>
+    <t>1_0;2_10;3_30;4_30;5_30;6_0</t>
+  </si>
+  <si>
+    <t>随机图标_随机图标概率</t>
+  </si>
+  <si>
+    <t>随机到图标得概率（万分比）</t>
+  </si>
+  <si>
+    <t>5_3000_1000</t>
+  </si>
+  <si>
+    <t>转轴上最低出现元素个数_随机到图标得概率（万分比）_随机图标变成wild概率</t>
+  </si>
+  <si>
+    <t>元素滚轴</t>
+  </si>
+  <si>
+    <t>1_2034002;2_2034003;3_2034004;4_2034005;5_2034006;6_2034007</t>
+  </si>
+  <si>
+    <t>元素id_元素滚轴</t>
+  </si>
+  <si>
+    <t>金蛇招财</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金钱兔模式特效</t>
+  </si>
+  <si>
+    <t>1,500</t>
+  </si>
+  <si>
+    <t>模式，概率假进金钱兔模式万分比</t>
+  </si>
+  <si>
+    <t>金钱兔</t>
+  </si>
+  <si>
+    <t>鼠鼠福福</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发福鼠模式特效</t>
+  </si>
+  <si>
+    <t>模式，概率假进福鼠模式万分比</t>
+  </si>
+  <si>
+    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
+  </si>
+  <si>
+    <t>2,0_1</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_1000|6_20_100</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
     <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
   </si>
   <si>
-    <t>随机图标_随机图标概率</t>
-  </si>
-  <si>
-    <t>随机到图标得概率（万分比）</t>
-  </si>
-  <si>
     <t>5_3000_2000</t>
   </si>
   <si>
-    <t>转轴上最低出现元素个数_随机到图标得概率（万分比）_随机图标变成wild概率</t>
-  </si>
-  <si>
-    <t>元素滚轴</t>
-  </si>
-  <si>
-    <t>1_2034002;2_2034003;3_2034004;4_2034005;5_2034006;6_2034007</t>
-  </si>
-  <si>
-    <t>元素id_元素滚轴</t>
-  </si>
-  <si>
-    <t>金蛇招财</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发金钱兔模式特效</t>
-  </si>
-  <si>
-    <t>模式，概率假进金钱兔模式万分比</t>
-  </si>
-  <si>
-    <t>金钱兔</t>
-  </si>
-  <si>
-    <t>鼠鼠福福</t>
-  </si>
-  <si>
-    <t>常规模式下，概率触发福鼠模式特效</t>
-  </si>
-  <si>
-    <t>模式，概率假进福鼠模式万分比</t>
-  </si>
-  <si>
-    <t>福鼠模式下，获得连线奖励奖返回常规模式</t>
-  </si>
-  <si>
-    <t>2,0_1</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400334,30200009_30200014</t>
+  </si>
+  <si>
+    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -764,12 +800,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -780,7 +816,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,6 +825,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -986,12 +1028,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1116,7 +1173,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1128,122 +1185,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1251,20 +1308,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1279,17 +1339,32 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1346,11 +1421,18 @@
     <cellStyle name="常规 80" xfId="50"/>
     <cellStyle name="常规 2" xfId="51"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1622,185 +1704,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <v>100100</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="10"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>100100</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="11">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="10"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>100100</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="10"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2">
@@ -1818,14 +1900,14 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="2">
@@ -1843,14 +1925,14 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -1868,96 +1950,96 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>102400</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>102400</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="10"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>102400</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="10"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="2">
@@ -1975,14 +2057,14 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -2000,98 +2082,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>5022007</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <v>102200</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="16"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="2">
         <v>5022008</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <v>102200</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="16"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
         <v>5021001</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <v>102100</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="2">
         <v>5021002</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="17">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2103,7 +2185,7 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2114,7 +2196,7 @@
       <c r="A20" s="2">
         <v>5018001</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="17">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2126,20 +2208,20 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
         <v>5018002</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="17">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2151,20 +2233,20 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="2">
         <v>5025001</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2176,20 +2258,20 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
         <v>5023005</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="17">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2201,20 +2283,20 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
         <v>5023008</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2226,20 +2308,20 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="15" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="2">
         <v>5023009</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2257,14 +2339,14 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="2">
         <v>5034001</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2276,20 +2358,20 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
         <v>5034002</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2301,20 +2383,20 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="18" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
         <v>5034003</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2326,20 +2408,20 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="18" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
         <v>5034004</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2351,20 +2433,20 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
         <v>5035001</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="17">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2376,24 +2458,24 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>71</v>
+      <c r="F30" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="2">
         <v>5035011</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -2401,73 +2483,273 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>71</v>
+      <c r="F31" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="2">
         <v>5036001</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="17">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>71</v>
+        <v>88</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:9">
+        <v>89</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="2">
         <v>5036002</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="17">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
-      </c>
-      <c r="F33" s="14" t="s">
         <v>90</v>
       </c>
+      <c r="F33" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="G33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A34" s="2">
+        <v>5028001</v>
+      </c>
+      <c r="B34" s="17">
+        <v>102800</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A35" s="2">
+        <v>5028002</v>
+      </c>
+      <c r="B35" s="17">
+        <v>102800</v>
+      </c>
+      <c r="C35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A36" s="2">
+        <v>5034011</v>
+      </c>
+      <c r="B36" s="17">
+        <v>103401</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A37" s="2">
+        <v>5034012</v>
+      </c>
+      <c r="B37" s="17">
+        <v>103402</v>
+      </c>
+      <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A38" s="2">
+        <v>5034013</v>
+      </c>
+      <c r="B38" s="17">
+        <v>103403</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A39" s="2">
+        <v>5034014</v>
+      </c>
+      <c r="B39" s="17">
+        <v>103404</v>
+      </c>
+      <c r="C39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A40" s="3">
+        <v>5020001</v>
+      </c>
+      <c r="B40" s="19">
+        <v>102000</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="19">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" ht="16.5" spans="1:10">
+      <c r="A41" s="3">
+        <v>5020002</v>
+      </c>
+      <c r="B41" s="19">
+        <v>102000</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="19">
+        <v>2</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:10">
+      <c r="E44" s="22"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E44">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2485,24 +2767,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2510,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2524,13 +2806,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2538,13 +2820,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2552,13 +2834,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2566,13 +2848,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2580,13 +2862,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2594,7 +2876,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2602,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2610,7 +2892,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2618,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2626,7 +2908,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2634,7 +2916,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2642,7 +2924,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2650,7 +2932,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2658,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2666,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2674,7 +2956,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2682,7 +2964,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2690,7 +2972,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2698,7 +2980,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2706,7 +2988,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2714,7 +2996,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2722,7 +3004,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2730,7 +3012,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2738,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2746,7 +3028,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2754,7 +3036,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2762,7 +3044,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2770,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2778,7 +3060,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2786,7 +3068,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2794,7 +3076,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2802,7 +3084,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2810,7 +3092,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2818,7 +3100,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2826,7 +3108,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2834,7 +3116,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2842,7 +3124,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2850,7 +3132,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2858,7 +3140,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2866,7 +3148,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2874,7 +3156,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2882,7 +3164,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2890,7 +3172,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2898,7 +3180,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2906,7 +3188,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="165">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -416,6 +416,54 @@
   </si>
   <si>
     <t>SpecialMode模式ID，中奖倍率大于x时回到常规模式</t>
+  </si>
+  <si>
+    <t>王牌dj</t>
+  </si>
+  <si>
+    <t>2,13,4_10_10000|5_15_1000|6_20_100</t>
+  </si>
+  <si>
+    <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>2_2_2_2_4_6_8_10_12_14_16_18_20_22_24_26_28_30</t>
+  </si>
+  <si>
+    <t>初始为2，2，2，2，每次销毁加2，到达最大值30时，之后每次都为30</t>
+  </si>
+  <si>
+    <t>虎虎生财</t>
+  </si>
+  <si>
+    <t>1_1;2_1;3_1;4_1;5_1;6_1</t>
+  </si>
+  <si>
+    <t>5_3000_2000</t>
+  </si>
+  <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>1020400334,30200009_30200014</t>
+  </si>
+  <si>
+    <t>30200003,30200007|30200008;30200004,30200007|30200008;30200005,30200007|30200006;30200006,30200007|30200008</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>2,10,3_12_10000|4_15_1000|5_20_100</t>
+  </si>
+  <si>
+    <t>免费游戏下，收集wild个数增加倍率值</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -767,6 +815,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -777,7 +826,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -989,12 +1037,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1119,7 +1182,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1131,34 +1194,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1246,7 +1309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1254,6 +1317,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1293,6 +1360,22 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1349,11 +1432,18 @@
     <cellStyle name="常规 80" xfId="50"/>
     <cellStyle name="常规 2" xfId="51"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1625,185 +1715,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="5" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="6" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="5"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="7"/>
+      <c r="H2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="12">
         <v>100100</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="12">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="10"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <v>100100</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="10"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="12">
         <v>100100</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="12">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="10"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2">
@@ -1821,14 +1911,14 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="16" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="2">
@@ -1846,14 +1936,14 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -1871,96 +1961,96 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="12">
         <v>102400</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="12">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="10"/>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="12">
         <v>102400</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="12">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="10"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="12">
         <v>102400</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="12">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="10"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="2">
@@ -1978,14 +2068,14 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="16" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -2003,98 +2093,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>5022007</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="18">
         <v>102200</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="18">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="16"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="2">
         <v>5022008</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="18">
         <v>102200</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="18">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="16"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
         <v>5021001</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="18">
         <v>102100</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="18">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="2">
         <v>5021002</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="18">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2106,7 +2196,7 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2117,7 +2207,7 @@
       <c r="A20" s="2">
         <v>5018001</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="18">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2129,20 +2219,20 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="16" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
         <v>5018002</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="18">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2154,20 +2244,20 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="16" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="2">
         <v>5025001</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="18">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2179,20 +2269,20 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="16" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
         <v>5023005</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="18">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2204,20 +2294,20 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="16" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
         <v>5023008</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="18">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2229,20 +2319,20 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="16" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
     </row>
     <row r="25" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="2">
         <v>5023009</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="18">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2260,14 +2350,14 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
     </row>
     <row r="26" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="2">
         <v>5034001</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="18">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2279,20 +2369,20 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
         <v>5034002</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="18">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2304,20 +2394,20 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="19" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
         <v>5034003</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="18">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2329,20 +2419,20 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="19" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
         <v>5034004</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="18">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2354,20 +2444,20 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="16" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
         <v>5035001</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="18">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2379,20 +2469,20 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="16" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
     </row>
     <row r="31" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="2">
         <v>5035011</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="18">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
@@ -2404,20 +2494,20 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="16" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
     </row>
     <row r="32" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="2">
         <v>5036001</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="18">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
@@ -2429,20 +2519,20 @@
       <c r="E32" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="16" t="s">
         <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:9">
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+    </row>
+    <row r="33" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="2">
         <v>5036002</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="18">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
@@ -2454,23 +2544,274 @@
       <c r="E33" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="16" t="s">
         <v>91</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A34" s="2">
+        <v>5028001</v>
+      </c>
+      <c r="B34" s="18">
+        <v>102800</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A35" s="2">
+        <v>5028002</v>
+      </c>
+      <c r="B35" s="18">
+        <v>102800</v>
+      </c>
+      <c r="C35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A36" s="2">
+        <v>5034011</v>
+      </c>
+      <c r="B36" s="18">
+        <v>103401</v>
+      </c>
+      <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A37" s="2">
+        <v>5034012</v>
+      </c>
+      <c r="B37" s="18">
+        <v>103402</v>
+      </c>
+      <c r="C37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+    </row>
+    <row r="38" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A38" s="2">
+        <v>5034013</v>
+      </c>
+      <c r="B38" s="18">
+        <v>103403</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+    </row>
+    <row r="39" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A39" s="2">
+        <v>5034014</v>
+      </c>
+      <c r="B39" s="18">
+        <v>103404</v>
+      </c>
+      <c r="C39" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A40" s="3">
+        <v>5020001</v>
+      </c>
+      <c r="B40" s="20">
+        <v>102000</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="20">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A41" s="3">
+        <v>5020002</v>
+      </c>
+      <c r="B41" s="20">
+        <v>102000</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="20">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+    </row>
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A42" s="3">
+        <v>5027001</v>
+      </c>
+      <c r="B42" s="20">
+        <v>102700</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="20">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+    </row>
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A43" s="3">
+        <v>5027002</v>
+      </c>
+      <c r="B43" s="20">
+        <v>102700</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="20">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+    </row>
+    <row r="44" ht="16.5" spans="1:10">
+      <c r="E44" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E44">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2488,24 +2829,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2513,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2527,13 +2868,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2541,13 +2882,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2555,13 +2896,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2569,13 +2910,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2583,13 +2924,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2597,7 +2938,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2605,7 +2946,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2613,7 +2954,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2621,7 +2962,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2629,7 +2970,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2637,7 +2978,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2645,7 +2986,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2653,7 +2994,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2661,7 +3002,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2669,7 +3010,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2677,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2685,7 +3026,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2693,7 +3034,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2701,7 +3042,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2709,7 +3050,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2717,7 +3058,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2725,7 +3066,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2733,7 +3074,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2741,7 +3082,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2749,7 +3090,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2757,7 +3098,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2765,7 +3106,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2773,7 +3114,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2781,7 +3122,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2789,7 +3130,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2797,7 +3138,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2805,7 +3146,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2813,7 +3154,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2821,7 +3162,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2829,7 +3170,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2837,7 +3178,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2845,7 +3186,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2853,7 +3194,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2861,7 +3202,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2869,7 +3210,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2877,7 +3218,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2885,7 +3226,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2893,7 +3234,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2901,7 +3242,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2909,7 +3250,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="172">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -464,6 +464,27 @@
   </si>
   <si>
     <t>免费游戏中，每收集3个百搭符号乘倍值将增加2（增加2后将清零重新收集），最多增加至20倍</t>
+  </si>
+  <si>
+    <t>10倍金牛</t>
+  </si>
+  <si>
+    <t>常规模式下，概率触发金牛赐福模式特效</t>
+  </si>
+  <si>
+    <t>金牛赐福模式下，有中奖连线时退出此模式</t>
+  </si>
+  <si>
+    <t>2,10000</t>
+  </si>
+  <si>
+    <t>模式ID，退出万分比</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>2_12_15_10000</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1037,27 +1058,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1182,7 +1188,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1194,34 +1200,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1309,7 +1315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1317,9 +1323,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1363,19 +1366,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="52">
@@ -1432,18 +1422,11 @@
     <cellStyle name="常规 80" xfId="50"/>
     <cellStyle name="常规 2" xfId="51"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="8" tint="0.799340800195319"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1715,185 +1698,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="9.50833333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
     <col min="5" max="5" width="61.75" customWidth="1"/>
     <col min="6" max="6" width="50.875" customWidth="1"/>
     <col min="7" max="7" width="74.7" customWidth="1"/>
-    <col min="8" max="8" width="26.3" style="6" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="26.3" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="7.81666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="7"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="10" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="9" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="7"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="2">
         <v>5001001</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>100100</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="12"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="2">
         <v>5001002</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>100100</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="12"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A7" s="2">
         <v>5001007</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>100100</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="12"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2">
@@ -1911,14 +1894,14 @@
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A9" s="2">
@@ -1936,14 +1919,14 @@
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A10" s="2">
@@ -1961,96 +1944,96 @@
       <c r="E10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A11" s="2">
         <v>5024001</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>102400</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A12" s="2">
         <v>5024002</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>102400</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="12"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="11"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A13" s="2">
         <v>5024007</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>102400</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="12"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A14" s="2">
@@ -2068,14 +2051,14 @@
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A15" s="2">
@@ -2093,98 +2076,98 @@
       <c r="E15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A16" s="2">
         <v>5022007</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>102200</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="18"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A17" s="2">
         <v>5022008</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>102200</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="18"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A18" s="2">
         <v>5021001</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>102100</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>4</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="18"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" ht="16.5" spans="1:10">
       <c r="A19" s="2">
         <v>5021002</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>102100</v>
       </c>
       <c r="C19" t="s">
@@ -2196,7 +2179,7 @@
       <c r="E19" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="15" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2207,7 +2190,7 @@
       <c r="A20" s="2">
         <v>5018001</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>101800</v>
       </c>
       <c r="C20" t="s">
@@ -2219,20 +2202,20 @@
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="2">
         <v>5018002</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>101800</v>
       </c>
       <c r="C21" t="s">
@@ -2244,20 +2227,20 @@
       <c r="E21" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="2">
         <v>5025001</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="17">
         <v>102500</v>
       </c>
       <c r="C22" t="s">
@@ -2269,20 +2252,20 @@
       <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="2">
         <v>5023005</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <v>102300</v>
       </c>
       <c r="C23" t="s">
@@ -2294,20 +2277,20 @@
       <c r="E23" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="2">
         <v>5023008</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="17">
         <v>102300</v>
       </c>
       <c r="C24" t="s">
@@ -2319,20 +2302,20 @@
       <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>65</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="2">
         <v>5023009</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <v>102300</v>
       </c>
       <c r="C25" t="s">
@@ -2350,14 +2333,14 @@
       <c r="G25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="2">
         <v>5034001</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="17">
         <v>103400</v>
       </c>
       <c r="C26" t="s">
@@ -2369,20 +2352,20 @@
       <c r="E26" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="2">
         <v>5034002</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="17">
         <v>103400</v>
       </c>
       <c r="C27" t="s">
@@ -2394,20 +2377,20 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="18" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="2">
         <v>5034003</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="17">
         <v>103400</v>
       </c>
       <c r="C28" t="s">
@@ -2419,20 +2402,20 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="18" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="2">
         <v>5034004</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="17">
         <v>103400</v>
       </c>
       <c r="C29" t="s">
@@ -2444,20 +2427,20 @@
       <c r="E29" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="2">
         <v>5035001</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="17">
         <v>103500</v>
       </c>
       <c r="C30" t="s">
@@ -2469,20 +2452,20 @@
       <c r="E30" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="15" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="2">
         <v>5035011</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="17">
         <v>103501</v>
       </c>
       <c r="C31" t="s">
@@ -2494,20 +2477,20 @@
       <c r="E31" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="15" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="2">
         <v>5036001</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <v>103600</v>
       </c>
       <c r="C32" t="s">
@@ -2519,20 +2502,20 @@
       <c r="E32" t="s">
         <v>88</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="15" t="s">
         <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="2">
         <v>5036002</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <v>103600</v>
       </c>
       <c r="C33" t="s">
@@ -2544,20 +2527,20 @@
       <c r="E33" t="s">
         <v>90</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="15" t="s">
         <v>91</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" customFormat="1" ht="16.5" spans="1:10">
       <c r="A34" s="2">
         <v>5028001</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>102800</v>
       </c>
       <c r="C34" t="s">
@@ -2569,20 +2552,20 @@
       <c r="E34" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="15" t="s">
         <v>94</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35" customFormat="1" ht="16.5" spans="1:10">
       <c r="A35" s="2">
         <v>5028002</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <v>102800</v>
       </c>
       <c r="C35" t="s">
@@ -2594,20 +2577,20 @@
       <c r="E35" t="s">
         <v>95</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="15" t="s">
         <v>96</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36" customFormat="1" ht="16.5" spans="1:10">
       <c r="A36" s="2">
         <v>5034011</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="17">
         <v>103401</v>
       </c>
       <c r="C36" t="s">
@@ -2619,20 +2602,20 @@
       <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>71</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37" customFormat="1" ht="16.5" spans="1:10">
       <c r="A37" s="2">
         <v>5034012</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="17">
         <v>103402</v>
       </c>
       <c r="C37" t="s">
@@ -2644,20 +2627,20 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="15" t="s">
         <v>99</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38" customFormat="1" ht="16.5" spans="1:10">
       <c r="A38" s="2">
         <v>5034013</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="17">
         <v>103403</v>
       </c>
       <c r="C38" t="s">
@@ -2669,20 +2652,20 @@
       <c r="E38" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="15" t="s">
         <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
     <row r="39" customFormat="1" ht="16.5" spans="1:10">
       <c r="A39" s="2">
         <v>5034014</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="17">
         <v>103404</v>
       </c>
       <c r="C39" t="s">
@@ -2694,121 +2677,182 @@
       <c r="E39" t="s">
         <v>79</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" s="15" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" s="3" customFormat="1" ht="18" customHeight="1" spans="1:10">
-      <c r="A40" s="3">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" s="2" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="A40" s="2">
         <v>5020001</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="17">
         <v>102000</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="17">
         <v>1</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G40" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="20"/>
-    </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A41" s="3">
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A41" s="2">
         <v>5020002</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="17">
         <v>102000</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="17">
         <v>2</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-    </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A42" s="3">
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A42" s="2">
         <v>5027001</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="17">
         <v>102700</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="20">
+      <c r="D42" s="17">
         <v>1</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-    </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A43" s="3">
+    </row>
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A43" s="2">
         <v>5027002</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="17">
         <v>102700</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="17">
         <v>2</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:10">
-      <c r="E44" s="24"/>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A44" s="2">
+        <v>5037001</v>
+      </c>
+      <c r="B44" s="17">
+        <v>103700</v>
+      </c>
+      <c r="C44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" ht="16.5" spans="1:10">
+      <c r="A45" s="2">
+        <v>5037002</v>
+      </c>
+      <c r="B45" s="17">
+        <v>103700</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A46" s="2">
+        <v>5031001</v>
+      </c>
+      <c r="B46" s="17">
+        <v>103100</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E44">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
     <cfRule type="expression" dxfId="0" priority="3">
@@ -2829,24 +2873,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2854,13 +2898,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2868,13 +2912,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2882,13 +2926,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2896,13 +2940,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2910,13 +2954,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2924,13 +2968,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2938,7 +2982,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2946,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2954,7 +2998,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2962,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2970,7 +3014,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2978,7 +3022,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2986,7 +3030,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2994,7 +3038,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3002,7 +3046,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3010,7 +3054,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3018,7 +3062,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3026,7 +3070,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3034,7 +3078,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3042,7 +3086,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3050,7 +3094,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3058,7 +3102,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3066,7 +3110,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3074,7 +3118,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3082,7 +3126,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3090,7 +3134,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3098,7 +3142,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3106,7 +3150,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3114,7 +3158,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3122,7 +3166,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3130,7 +3174,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3138,7 +3182,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3146,7 +3190,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3154,7 +3198,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3162,7 +3206,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3170,7 +3214,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3178,7 +3222,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3186,7 +3230,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3194,7 +3238,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3202,7 +3246,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3210,7 +3254,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3218,7 +3262,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3226,7 +3270,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3234,7 +3278,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3242,7 +3286,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3250,7 +3294,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -322,7 +322,7 @@
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>2,11,3_10_10000|4_15_1000|5_20_100</t>
+    <t>2,11,3_10_10000|4_15_1000|5_25_100</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -767,17 +767,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="178">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -322,7 +322,7 @@
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>2,11,3_10_10000|4_15_1000|5_20_100</t>
+    <t>2,11,3_10_10000|4_15_1000|5_25_100</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -485,6 +485,24 @@
   </si>
   <si>
     <t>2_12_15_10000</t>
+  </si>
+  <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>2_12_5_10000</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>免费游戏每局游戏获得随机乘倍值</t>
+  </si>
+  <si>
+    <t>2,1_2000|2_3000|3_3000|4_1500|5_500</t>
+  </si>
+  <si>
+    <t>模式，倍数_获得倍率万分比|倍数_获得倍率万分比|倍数_获得倍率万分比</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -836,13 +854,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1698,7 +1716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -2847,6 +2865,56 @@
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A47" s="2">
+        <v>5040001</v>
+      </c>
+      <c r="B47" s="17">
+        <v>104000</v>
+      </c>
+      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A48" s="2">
+        <v>5039001</v>
+      </c>
+      <c r="B48" s="17">
+        <v>103900</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>119</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2873,24 +2941,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2898,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2912,13 +2980,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2926,13 +2994,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2940,13 +3008,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2954,13 +3022,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2968,13 +3036,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2982,7 +3050,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2990,7 +3058,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2998,7 +3066,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3006,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3014,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3022,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3030,7 +3098,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3038,7 +3106,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3046,7 +3114,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3054,7 +3122,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3062,7 +3130,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3070,7 +3138,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3078,7 +3146,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3086,7 +3154,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3094,7 +3162,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3102,7 +3170,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3110,7 +3178,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3118,7 +3186,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3126,7 +3194,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3134,7 +3202,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3142,7 +3210,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3150,7 +3218,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3158,7 +3226,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3166,7 +3234,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3174,7 +3242,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3182,7 +3250,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3190,7 +3258,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3198,7 +3266,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3206,7 +3274,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3214,7 +3282,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3222,7 +3290,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3230,7 +3298,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3238,7 +3306,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3246,7 +3314,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3254,7 +3322,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3262,7 +3330,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3270,7 +3338,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3278,7 +3346,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3286,7 +3354,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3294,7 +3362,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="183">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -503,6 +503,21 @@
   </si>
   <si>
     <t>模式，倍数_获得倍率万分比|倍数_获得倍率万分比|倍数_获得倍率万分比</t>
+  </si>
+  <si>
+    <t>热血足球</t>
+  </si>
+  <si>
+    <t>2_14_1_10000</t>
+  </si>
+  <si>
+    <t>免费模式下，积满能量值获得奖金乘倍值</t>
+  </si>
+  <si>
+    <t>2,6_2|8_4|10_6|12_8|14_10|16_12|16_14</t>
+  </si>
+  <si>
+    <t>模式，能量值(初始能量值为6，每次积满能量后增加2，同时清空能量值从新累计)_倍数（每次积满能量后倍数+2）</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -854,7 +869,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -865,7 +880,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1716,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -2915,6 +2930,56 @@
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A49" s="2">
+        <v>5016001</v>
+      </c>
+      <c r="B49" s="17">
+        <v>101600</v>
+      </c>
+      <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A50" s="2">
+        <v>5016002</v>
+      </c>
+      <c r="B50" s="17">
+        <v>101600</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>124</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -2941,24 +3006,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2966,13 +3031,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2980,13 +3045,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2994,13 +3059,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3008,13 +3073,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3022,13 +3087,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3036,13 +3101,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3050,7 +3115,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3058,7 +3123,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3066,7 +3131,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3074,7 +3139,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3082,7 +3147,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3090,7 +3155,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3098,7 +3163,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3106,7 +3171,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3114,7 +3179,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3122,7 +3187,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3130,7 +3195,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3138,7 +3203,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3146,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3154,7 +3219,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3162,7 +3227,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3170,7 +3235,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3178,7 +3243,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3186,7 +3251,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3194,7 +3259,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3202,7 +3267,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3210,7 +3275,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3218,7 +3283,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3226,7 +3291,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3234,7 +3299,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3242,7 +3307,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3250,7 +3315,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3258,7 +3323,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3266,7 +3331,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3274,7 +3339,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3282,7 +3347,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3290,7 +3355,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3298,7 +3363,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3306,7 +3371,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3314,7 +3379,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3322,7 +3387,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3330,7 +3395,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3338,7 +3403,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3346,7 +3411,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3354,7 +3419,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3362,7 +3427,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="191">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -518,6 +518,30 @@
   </si>
   <si>
     <t>模式，能量值(初始能量值为6，每次积满能量后增加2，同时清空能量值从新累计)_倍数（每次积满能量后倍数+2）</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>手动选择小游戏：中奖ID,小游戏1_小游戏2_小游戏3|中奖ID,小游戏1_小游戏2……</t>
+  </si>
+  <si>
+    <t>1015400314,30150001_30150002_30150003</t>
+  </si>
+  <si>
+    <t>BaseElementReward表中中奖ID，小游戏1_小游戏2_小游戏3|……</t>
+  </si>
+  <si>
+    <t>免费递增奖励倍数模式下，每次免费旋转结算时原赔率乘以此倍率值</t>
+  </si>
+  <si>
+    <t>7_5</t>
+  </si>
+  <si>
+    <t>免费游戏中，初始获得5的乘倍值，每次旋转结算后乘倍值曾加5，最多可增加值100</t>
+  </si>
+  <si>
+    <t>2_15_1_10000</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -869,7 +893,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -880,7 +904,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1731,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -2980,6 +3004,207 @@
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A51" s="2">
+        <v>5015001</v>
+      </c>
+      <c r="B51" s="17">
+        <v>101500</v>
+      </c>
+      <c r="C51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A52" s="2">
+        <v>5015002</v>
+      </c>
+      <c r="B52" s="17">
+        <v>101500</v>
+      </c>
+      <c r="C52" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" t="s">
+        <v>131</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G52" t="s">
+        <v>133</v>
+      </c>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A53" s="2">
+        <v>5015003</v>
+      </c>
+      <c r="B53" s="17">
+        <v>101500</v>
+      </c>
+      <c r="C53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A54" s="2"/>
+      <c r="B54" s="17"/>
+      <c r="D54" s="1"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A55" s="2"/>
+      <c r="B55" s="17"/>
+      <c r="D55" s="1"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A56" s="2"/>
+      <c r="B56" s="17"/>
+      <c r="D56" s="1"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A57" s="2"/>
+      <c r="B57" s="17"/>
+      <c r="D57" s="1"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A58" s="2"/>
+      <c r="B58" s="17"/>
+      <c r="D58" s="1"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A59" s="2"/>
+      <c r="B59" s="17"/>
+      <c r="D59" s="1"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A60" s="2"/>
+      <c r="B60" s="17"/>
+      <c r="D60" s="1"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A61" s="2"/>
+      <c r="B61" s="17"/>
+      <c r="D61" s="1"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A62" s="2"/>
+      <c r="B62" s="17"/>
+      <c r="D62" s="1"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A63" s="2"/>
+      <c r="B63" s="17"/>
+      <c r="D63" s="1"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A64" s="2"/>
+      <c r="B64" s="17"/>
+      <c r="D64" s="1"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A65" s="2"/>
+      <c r="B65" s="17"/>
+      <c r="D65" s="1"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A66" s="2"/>
+      <c r="B66" s="17"/>
+      <c r="D66" s="1"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A67" s="2"/>
+      <c r="B67" s="17"/>
+      <c r="D67" s="1"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3006,24 +3231,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3031,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3045,13 +3270,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3059,13 +3284,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3073,13 +3298,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3087,13 +3312,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3101,13 +3326,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3115,7 +3340,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3123,7 +3348,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3131,7 +3356,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3139,7 +3364,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3147,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3155,7 +3380,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3163,7 +3388,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3171,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3179,7 +3404,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3187,7 +3412,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3195,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3203,7 +3428,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3211,7 +3436,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3219,7 +3444,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3227,7 +3452,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3235,7 +3460,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3243,7 +3468,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3251,7 +3476,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3259,7 +3484,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3267,7 +3492,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3275,7 +3500,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3283,7 +3508,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3291,7 +3516,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3299,7 +3524,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3307,7 +3532,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3315,7 +3540,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3323,7 +3548,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3331,7 +3556,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3339,7 +3564,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3347,7 +3572,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3355,7 +3580,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3363,7 +3588,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3371,7 +3596,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3379,7 +3604,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3387,7 +3612,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3395,7 +3620,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3403,7 +3628,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3411,7 +3636,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3419,7 +3644,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3427,7 +3652,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="194">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -472,13 +472,22 @@
     <t>常规模式下，概率触发金牛赐福模式特效</t>
   </si>
   <si>
-    <t>金牛赐福模式下，有中奖连线时退出此模式</t>
-  </si>
-  <si>
-    <t>2,10000</t>
-  </si>
-  <si>
-    <t>模式ID，退出万分比</t>
+    <t>金牛赐福模式下，玩家获得全屏奖出现的元素及权重</t>
+  </si>
+  <si>
+    <t>1_10|2_10|3_5|4_1</t>
+  </si>
+  <si>
+    <t>元素id_出现的权重_转出全屏奖的次数</t>
+  </si>
+  <si>
+    <t>金牛赐福模式下，玩家获得全屏奖时旋转的次数</t>
+  </si>
+  <si>
+    <t>3_1|4_1|5_1</t>
+  </si>
+  <si>
+    <t>次数_权重</t>
   </si>
   <si>
     <t>绿巨人</t>
@@ -1755,7 +1764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -2882,38 +2891,38 @@
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:10">
       <c r="A46" s="2">
-        <v>5031001</v>
+        <v>5037003</v>
       </c>
       <c r="B46" s="17">
-        <v>103100</v>
+        <v>103700</v>
       </c>
       <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" t="s">
         <v>114</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>33</v>
       </c>
       <c r="F46" s="15" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:10">
       <c r="A47" s="2">
-        <v>5040001</v>
+        <v>5031001</v>
       </c>
       <c r="B47" s="17">
-        <v>104000</v>
+        <v>103100</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -2922,7 +2931,7 @@
         <v>33</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>35</v>
@@ -2932,116 +2941,116 @@
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:10">
       <c r="A48" s="2">
-        <v>5039001</v>
+        <v>5040001</v>
       </c>
       <c r="B48" s="17">
-        <v>103900</v>
+        <v>104000</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D48" s="1">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="F48" s="15" t="s">
         <v>120</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:9">
       <c r="A49" s="2">
-        <v>5016001</v>
+        <v>5039001</v>
       </c>
       <c r="B49" s="17">
-        <v>101600</v>
+        <v>103900</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="F49" s="15" t="s">
         <v>123</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:9">
       <c r="A50" s="2">
-        <v>5016002</v>
+        <v>5016001</v>
       </c>
       <c r="B50" s="17">
         <v>101600</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:9">
       <c r="A51" s="2">
-        <v>5015001</v>
+        <v>5016002</v>
       </c>
       <c r="B51" s="17">
-        <v>101500</v>
+        <v>101600</v>
       </c>
       <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
         <v>127</v>
       </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F51" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="G51" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:9">
       <c r="A52" s="2">
-        <v>5015002</v>
+        <v>5015001</v>
       </c>
       <c r="B52" s="17">
         <v>101500</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="s">
         <v>131</v>
@@ -3049,7 +3058,7 @@
       <c r="F52" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H52" s="5"/>
@@ -3057,35 +3066,51 @@
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:9">
       <c r="A53" s="2">
-        <v>5015003</v>
+        <v>5015002</v>
       </c>
       <c r="B53" s="17">
         <v>101500</v>
       </c>
       <c r="C53" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>35</v>
+        <v>135</v>
+      </c>
+      <c r="G53" t="s">
+        <v>136</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A54" s="2"/>
-      <c r="B54" s="17"/>
-      <c r="D54" s="1"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="1"/>
+      <c r="A54" s="2">
+        <v>5015003</v>
+      </c>
+      <c r="B54" s="17">
+        <v>101500</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
     </row>
@@ -3205,6 +3230,15 @@
       <c r="G67" s="1"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
+    </row>
+    <row r="68" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A68" s="2"/>
+      <c r="B68" s="17"/>
+      <c r="D68" s="1"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3231,24 +3265,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3256,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3270,13 +3304,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3284,13 +3318,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3298,13 +3332,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3312,13 +3346,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3326,13 +3360,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3340,7 +3374,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3348,7 +3382,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3356,7 +3390,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3364,7 +3398,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3372,7 +3406,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3380,7 +3414,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3388,7 +3422,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3396,7 +3430,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3404,7 +3438,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3412,7 +3446,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3420,7 +3454,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3428,7 +3462,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3436,7 +3470,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3444,7 +3478,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3452,7 +3486,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3460,7 +3494,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3468,7 +3502,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3476,7 +3510,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3484,7 +3518,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3492,7 +3526,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3500,7 +3534,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3508,7 +3542,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3516,7 +3550,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3524,7 +3558,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3532,7 +3566,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3540,7 +3574,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3548,7 +3582,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3556,7 +3590,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3564,7 +3598,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3572,7 +3606,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3580,7 +3614,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3588,7 +3622,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3596,7 +3630,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3604,7 +3638,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3612,7 +3646,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3620,7 +3654,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3628,7 +3662,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3636,7 +3670,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3644,7 +3678,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3652,7 +3686,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="199">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -322,7 +322,7 @@
     <t>寒冰王座</t>
   </si>
   <si>
-    <t>2,11,3_10_10000|4_15_1000|5_25_100</t>
+    <t>2,11,3_10_10000|4_15_10000|5_25_10000</t>
   </si>
   <si>
     <t>蒸汽时代</t>
@@ -421,7 +421,7 @@
     <t>王牌dj</t>
   </si>
   <si>
-    <t>2,13,4_10_10000|5_15_1000|6_20_100</t>
+    <t>2,13,4_10_10000|5_15_10000|6_20_10000</t>
   </si>
   <si>
     <t>带wild中奖对应得中奖倍率，原赔率乘以此倍率值</t>
@@ -454,7 +454,7 @@
     <t>象财神</t>
   </si>
   <si>
-    <t>2,10,3_12_10000|4_15_1000|5_20_100</t>
+    <t>2,10,3_12_10000|4_15_10000|5_20_10000</t>
   </si>
   <si>
     <t>免费游戏下，收集wild个数增加倍率值</t>
@@ -508,10 +508,10 @@
     <t>免费游戏每局游戏获得随机乘倍值</t>
   </si>
   <si>
-    <t>2,1_2000|2_3000|3_3000|4_1500|5_500</t>
-  </si>
-  <si>
-    <t>模式，倍数_获得倍率万分比|倍数_获得倍率万分比|倍数_获得倍率万分比</t>
+    <t>1_2000|2_3000|3_3000|4_1500|5_500</t>
+  </si>
+  <si>
+    <t>倍数_获得倍率万分比|倍数_获得倍率万分比|倍数_获得倍率万分比</t>
   </si>
   <si>
     <t>热血足球</t>
@@ -550,7 +550,22 @@
     <t>免费游戏中，初始获得5的乘倍值，每次旋转结算后乘倍值曾加5，最多可增加值100</t>
   </si>
   <si>
-    <t>2_15_1_10000</t>
+    <t>寻宝黄金城</t>
+  </si>
+  <si>
+    <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
+  </si>
+  <si>
+    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
+  </si>
+  <si>
+    <t>常规模式下，金矿符号转换为百搭符号或黏性百搭符号</t>
+  </si>
+  <si>
+    <t>29_9_1|41_9_1|53_9_1</t>
+  </si>
+  <si>
+    <t>元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -907,12 +922,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3105,8 +3120,8 @@
       <c r="E54" t="s">
         <v>33</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>137</v>
+      <c r="F54" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -3115,29 +3130,77 @@
       <c r="I54" s="5"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A55" s="2"/>
-      <c r="B55" s="17"/>
-      <c r="D55" s="1"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="1"/>
+      <c r="A55" s="2">
+        <v>5026001</v>
+      </c>
+      <c r="B55" s="17">
+        <v>102600</v>
+      </c>
+      <c r="C55" t="s">
+        <v>137</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A56" s="2"/>
-      <c r="B56" s="17"/>
-      <c r="D56" s="1"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="1"/>
+      <c r="A56" s="2">
+        <v>5026002</v>
+      </c>
+      <c r="B56" s="17">
+        <v>102600</v>
+      </c>
+      <c r="C56" t="s">
+        <v>137</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A57" s="2"/>
-      <c r="B57" s="17"/>
-      <c r="D57" s="1"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="1"/>
+      <c r="A57" s="2">
+        <v>5026003</v>
+      </c>
+      <c r="B57" s="17">
+        <v>102600</v>
+      </c>
+      <c r="C57" t="s">
+        <v>137</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
@@ -3265,24 +3328,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3290,13 +3353,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3304,13 +3367,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3318,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3332,13 +3395,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3346,13 +3409,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3360,13 +3423,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3374,7 +3437,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3382,7 +3445,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3390,7 +3453,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3398,7 +3461,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3406,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3414,7 +3477,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3422,7 +3485,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3430,7 +3493,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3438,7 +3501,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3446,7 +3509,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3454,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3462,7 +3525,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3470,7 +3533,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3478,7 +3541,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3486,7 +3549,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3494,7 +3557,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3502,7 +3565,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3510,7 +3573,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3518,7 +3581,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3526,7 +3589,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3534,7 +3597,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3542,7 +3605,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3550,7 +3613,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3558,7 +3621,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3566,7 +3629,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3574,7 +3637,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3582,7 +3645,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3590,7 +3653,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3598,7 +3661,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3606,7 +3669,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3614,7 +3677,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3622,7 +3685,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3630,7 +3693,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3638,7 +3701,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3646,7 +3709,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3654,7 +3717,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3662,7 +3725,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3670,7 +3733,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3678,7 +3741,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3686,7 +3749,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="13785" windowHeight="11175"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="215">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -566,6 +566,54 @@
   </si>
   <si>
     <t>元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重</t>
+  </si>
+  <si>
+    <t>澳门壕梦</t>
+  </si>
+  <si>
+    <t>2,13,4_15_10000|5_17_10000|6_19_10000</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，目标图案，目标图案个数_中奖增加免费次数_中奖万分比</t>
+  </si>
+  <si>
+    <t>免费模式下，获得连续中奖次数对应的中奖倍数，原倍率上乘以此倍率</t>
+  </si>
+  <si>
+    <t>2,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10|11_11|12_12|…….</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖次数_中奖倍率|中奖次数_中奖倍率|…….</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>游戏开局就为第一层，第一层的常规和免费模式下，累计获得15个过关图标1会进入第二层，且过关图标1超过15个时，多余的会转变为过关图标2</t>
+  </si>
+  <si>
+    <t>3,16_15_17</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标1_累计获得次数_过关图标2</t>
+  </si>
+  <si>
+    <t>第二层的常规和免费模式下，累计获得15个过关图标2会进入第三层，且过关图标2超过15个时，多余的会转变为过关图标3</t>
+  </si>
+  <si>
+    <t>2,17_15_18</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标2_累计获得次数_过关图标2</t>
+  </si>
+  <si>
+    <t>第三层的常规和免费模式下，累计获得15个过关图标2会进入第一层，且过关图标3超过15个时，多余的会归零</t>
+  </si>
+  <si>
+    <t>1,18_15</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标3_累计获得次数</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -922,12 +970,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3205,47 +3253,127 @@
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A58" s="2"/>
-      <c r="B58" s="17"/>
-      <c r="D58" s="1"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="1"/>
+      <c r="A58" s="2">
+        <v>5050001</v>
+      </c>
+      <c r="B58" s="17">
+        <v>105000</v>
+      </c>
+      <c r="C58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A59" s="2"/>
-      <c r="B59" s="17"/>
-      <c r="D59" s="1"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="1"/>
+      <c r="A59" s="2">
+        <v>5050002</v>
+      </c>
+      <c r="B59" s="17">
+        <v>105000</v>
+      </c>
+      <c r="C59" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2</v>
+      </c>
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A60" s="2"/>
-      <c r="B60" s="17"/>
-      <c r="D60" s="1"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="1"/>
+      <c r="A60" s="2">
+        <v>5051001</v>
+      </c>
+      <c r="B60" s="17">
+        <v>105100</v>
+      </c>
+      <c r="C60" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A61" s="2"/>
-      <c r="B61" s="17"/>
-      <c r="D61" s="1"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="1"/>
+      <c r="A61" s="2">
+        <v>5051002</v>
+      </c>
+      <c r="B61" s="17">
+        <v>105100</v>
+      </c>
+      <c r="C61" t="s">
+        <v>149</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="2"/>
-      <c r="B62" s="17"/>
-      <c r="D62" s="1"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="1"/>
+      <c r="A62" s="2">
+        <v>5051003</v>
+      </c>
+      <c r="B62" s="17">
+        <v>105100</v>
+      </c>
+      <c r="C62" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" t="s">
+        <v>156</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
     </row>
@@ -3328,24 +3456,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D1" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3353,13 +3481,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3367,13 +3495,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3381,13 +3509,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3395,13 +3523,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3409,13 +3537,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3423,13 +3551,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3437,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3445,7 +3573,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3453,7 +3581,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3461,7 +3589,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3469,7 +3597,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3477,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3485,7 +3613,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3493,7 +3621,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3501,7 +3629,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3509,7 +3637,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3517,7 +3645,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3525,7 +3653,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3533,7 +3661,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3541,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3549,7 +3677,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3557,7 +3685,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3565,7 +3693,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3573,7 +3701,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3581,7 +3709,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3589,7 +3717,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3597,7 +3725,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3605,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3613,7 +3741,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3621,7 +3749,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3629,7 +3757,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3637,7 +3765,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3645,7 +3773,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3653,7 +3781,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3661,7 +3789,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3669,7 +3797,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3677,7 +3805,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3685,7 +3813,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3693,7 +3821,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3701,7 +3829,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3709,7 +3837,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3717,7 +3845,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3725,7 +3853,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3733,7 +3861,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3741,7 +3869,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3749,7 +3877,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13785" windowHeight="11175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -965,13 +965,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1444,7 +1444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1491,9 +1491,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1827,7 +1824,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -2506,7 +2503,7 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="15" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2531,7 +2528,7 @@
       <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="15" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2929,7 +2926,7 @@
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
     </row>
-    <row r="45" ht="16.5" spans="1:10">
+    <row r="45" customFormat="1" ht="16.5" spans="1:10">
       <c r="A45" s="2">
         <v>5037002</v>
       </c>
@@ -2951,6 +2948,8 @@
       <c r="G45" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:10">
       <c r="A46" s="2">
@@ -3377,68 +3376,14 @@
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A63" s="2"/>
-      <c r="B63" s="17"/>
-      <c r="D63" s="1"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-    </row>
-    <row r="64" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A64" s="2"/>
-      <c r="B64" s="17"/>
-      <c r="D64" s="1"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-    </row>
-    <row r="65" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A65" s="2"/>
-      <c r="B65" s="17"/>
-      <c r="D65" s="1"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-    </row>
-    <row r="66" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A66" s="2"/>
-      <c r="B66" s="17"/>
-      <c r="D66" s="1"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-    </row>
-    <row r="67" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A67" s="2"/>
-      <c r="B67" s="17"/>
-      <c r="D67" s="1"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-    </row>
-    <row r="68" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A68" s="2"/>
-      <c r="B68" s="17"/>
-      <c r="D68" s="1"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(MID($A2,1,4),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:C4 H1:I1 I2 H3:I4">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="214">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -554,9 +554,6 @@
   </si>
   <si>
     <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
-  </si>
-  <si>
-    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
   </si>
   <si>
     <t>常规模式下，金矿符号转换为百搭符号或黏性百搭符号</t>
@@ -965,13 +962,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1824,7 +1821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -3203,7 +3200,7 @@
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
-        <v>5026002</v>
+        <v>5026003</v>
       </c>
       <c r="B56" s="17">
         <v>102600</v>
@@ -3212,169 +3209,144 @@
         <v>137</v>
       </c>
       <c r="D56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>35</v>
+      <c r="F56" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
-        <v>5026003</v>
+        <v>5050001</v>
       </c>
       <c r="B57" s="17">
-        <v>102600</v>
+        <v>105000</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
-        <v>5050001</v>
+        <v>5050002</v>
       </c>
       <c r="B58" s="17">
         <v>105000</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5050002</v>
+        <v>5051001</v>
       </c>
       <c r="B59" s="17">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051001</v>
+        <v>5051002</v>
       </c>
       <c r="B60" s="17">
         <v>105100</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5051002</v>
+        <v>5051003</v>
       </c>
       <c r="B61" s="17">
         <v>105100</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
-    </row>
-    <row r="62" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A62" s="2">
-        <v>5051003</v>
-      </c>
-      <c r="B62" s="17">
-        <v>105100</v>
-      </c>
-      <c r="C62" t="s">
-        <v>149</v>
-      </c>
-      <c r="D62" s="1">
-        <v>3</v>
-      </c>
-      <c r="E62" t="s">
-        <v>156</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3401,24 +3373,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" t="s">
         <v>159</v>
-      </c>
-      <c r="D1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" t="s">
         <v>161</v>
       </c>
-      <c r="B2" t="s">
-        <v>162</v>
-      </c>
       <c r="D2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" t="s">
         <v>161</v>
-      </c>
-      <c r="E2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3426,13 +3398,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3440,13 +3412,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3454,13 +3426,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3468,13 +3440,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3482,13 +3454,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3496,13 +3468,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3510,7 +3482,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3518,7 +3490,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3526,7 +3498,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3534,7 +3506,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3542,7 +3514,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3550,7 +3522,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3558,7 +3530,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3566,7 +3538,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3574,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3582,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3590,7 +3562,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3598,7 +3570,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3606,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3614,7 +3586,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3622,7 +3594,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3630,7 +3602,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3638,7 +3610,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3646,7 +3618,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3654,7 +3626,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3662,7 +3634,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3670,7 +3642,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3678,7 +3650,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3686,7 +3658,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3694,7 +3666,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3702,7 +3674,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3710,7 +3682,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3718,7 +3690,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3726,7 +3698,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3734,7 +3706,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3742,7 +3714,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3750,7 +3722,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3758,7 +3730,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3766,7 +3738,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3774,7 +3746,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3782,7 +3754,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3790,7 +3762,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3798,7 +3770,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3806,7 +3778,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3814,7 +3786,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3822,7 +3794,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/SpecialPlay.xlsx
+++ b/slots/resources/sample/SpecialPlay.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21000" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialPlay" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="236">
   <si>
     <t>被动游戏ID</t>
   </si>
@@ -553,67 +553,130 @@
     <t>寻宝黄金城</t>
   </si>
   <si>
+    <t>1,1_10;2,2_20</t>
+  </si>
+  <si>
+    <t>常规模式下，金矿符号转换为百搭符号或黏性百搭符号</t>
+  </si>
+  <si>
+    <t>29_9_1|41_9_1|53_9_1</t>
+  </si>
+  <si>
+    <t>元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重</t>
+  </si>
+  <si>
+    <t>澳门壕梦</t>
+  </si>
+  <si>
+    <t>4,13,4_15_10000|5_17_10000|6_19_10000</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，目标图案，目标图案个数_中奖增加免费次数_中奖万分比</t>
+  </si>
+  <si>
+    <t>免费模式下，获得连续中奖次数对应的中奖倍数，原倍率上乘以此倍率</t>
+  </si>
+  <si>
+    <t>4,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10|11_11|12_12|…….</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，中奖次数_中奖倍率|中奖次数_中奖倍率|…….</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>游戏开局就为第一层，第一层的常规和免费模式下，累计获得15个过关图标1会进入第二层，且过关图标1超过15个时，多余的会转变为过关图标2</t>
+  </si>
+  <si>
+    <t>3,16_15_17</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标1_累计获得次数_过关图标2</t>
+  </si>
+  <si>
+    <t>第二层的常规和免费模式下，累计获得15个过关图标2会进入第三层，且过关图标2超过15个时，多余的会转变为过关图标3</t>
+  </si>
+  <si>
+    <t>2,17_15_18</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标2_累计获得次数_过关图标2</t>
+  </si>
+  <si>
+    <t>第三层的常规和免费模式下，累计获得15个过关图标2会进入第一层，且过关图标3超过15个时，多余的会归零</t>
+  </si>
+  <si>
+    <t>1,18_15</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID，过关图标3_累计获得次数</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>免费模式下，乘倍率随着中奖次数增加</t>
+  </si>
+  <si>
+    <t>SpecialMode模式ID,中奖次数_中奖倍率|中奖次数_中奖倍率|……</t>
+  </si>
+  <si>
+    <t>4,13,4_8_10000|5_10_10000|6_12_10000</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>出现招财猫符号时，乘倍值+2,出现多个此符号，倍数相加</t>
+  </si>
+  <si>
+    <t>11_2</t>
+  </si>
+  <si>
+    <t>符号id_乘倍值，普通模式每局结算乘倍值清零，免费模式乘倍值将累加</t>
+  </si>
+  <si>
+    <t>13,4_10_10000|5_12_10000|6_14_10000</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>11_3_10_10000|4_12_10000|5_14_10000</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
     <t>1,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10;2,1_2|2_4|3_6|4_8|5_10|6_12|7_14|8_16|9_18|10_20</t>
   </si>
   <si>
-    <t>2,13,4_12_10000|5_14_10000|6_16_10000</t>
-  </si>
-  <si>
-    <t>常规模式下，金矿符号转换为百搭符号或黏性百搭符号</t>
-  </si>
-  <si>
-    <t>29_9_1|41_9_1|53_9_1</t>
-  </si>
-  <si>
-    <t>元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重|元素id_百搭符号权重_黏性百搭符号权重</t>
-  </si>
-  <si>
-    <t>澳门壕梦</t>
-  </si>
-  <si>
-    <t>2,13,4_15_10000|5_17_10000|6_19_10000</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，目标图案，目标图案个数_中奖增加免费次数_中奖万分比</t>
-  </si>
-  <si>
-    <t>免费模式下，获得连续中奖次数对应的中奖倍数，原倍率上乘以此倍率</t>
-  </si>
-  <si>
-    <t>2,1_1|2_2|3_3|4_4|5_5|6_6|7_7|8_8|9_9|10_10|11_11|12_12|…….</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，中奖次数_中奖倍率|中奖次数_中奖倍率|…….</t>
-  </si>
-  <si>
-    <t>糖果派对</t>
-  </si>
-  <si>
-    <t>游戏开局就为第一层，第一层的常规和免费模式下，累计获得15个过关图标1会进入第二层，且过关图标1超过15个时，多余的会转变为过关图标2</t>
-  </si>
-  <si>
-    <t>3,16_15_17</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标1_累计获得次数_过关图标2</t>
-  </si>
-  <si>
-    <t>第二层的常规和免费模式下，累计获得15个过关图标2会进入第三层，且过关图标2超过15个时，多余的会转变为过关图标3</t>
-  </si>
-  <si>
-    <t>2,17_15_18</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标2_累计获得次数_过关图标2</t>
-  </si>
-  <si>
-    <t>第三层的常规和免费模式下，累计获得15个过关图标2会进入第一层，且过关图标3超过15个时，多余的会归零</t>
-  </si>
-  <si>
-    <t>1,18_15</t>
-  </si>
-  <si>
-    <t>SpecialMode模式ID，过关图标3_累计获得次数</t>
+    <t>3_10_10000|4_12_10000|5_14_10000</t>
+  </si>
+  <si>
+    <t>常规模式下，金框符号转换为百搭符号</t>
+  </si>
+  <si>
+    <t>9_1_1</t>
+  </si>
+  <si>
+    <t>元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重|元素id_金框符号权重_百搭符号权重</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>3_10_10000</t>
+  </si>
+  <si>
+    <t>相同位置中奖连续消除2次，此位置处获得x2，之后在此位置消除，每次消除乘倍值+2，最多增加至x32</t>
+  </si>
+  <si>
+    <t>2_32</t>
+  </si>
+  <si>
+    <t>初始倍数_最高倍数</t>
   </si>
   <si>
     <t>旋转标识</t>
@@ -1824,7 +1887,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="9.50833333333333" style="4" customWidth="1"/>
@@ -3203,7 +3266,7 @@
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="2">
-        <v>5026002</v>
+        <v>5026003</v>
       </c>
       <c r="B56" s="17">
         <v>102600</v>
@@ -3212,169 +3275,419 @@
         <v>137</v>
       </c>
       <c r="D56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>35</v>
+      <c r="F56" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="2">
-        <v>5026003</v>
+        <v>5050001</v>
       </c>
       <c r="B57" s="17">
-        <v>102600</v>
+        <v>105000</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="2">
-        <v>5050001</v>
+        <v>5050002</v>
       </c>
       <c r="B58" s="17">
         <v>105000</v>
       </c>
       <c r="C58" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:9">
       <c r="A59" s="2">
-        <v>5050002</v>
+        <v>5051001</v>
       </c>
       <c r="B59" s="17">
-        <v>105000</v>
+        <v>105100</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
     </row>
     <row r="60" customFormat="1" ht="16.5" spans="1:9">
       <c r="A60" s="2">
-        <v>5051001</v>
+        <v>5051002</v>
       </c>
       <c r="B60" s="17">
         <v>105100</v>
       </c>
       <c r="C60" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
     </row>
     <row r="61" customFormat="1" ht="16.5" spans="1:9">
       <c r="A61" s="2">
-        <v>5051002</v>
+        <v>5051003</v>
       </c>
       <c r="B61" s="17">
         <v>105100</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D61" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
     </row>
     <row r="62" customFormat="1" ht="16.5" spans="1:9">
       <c r="A62" s="2">
-        <v>5051003</v>
+        <v>5054001</v>
       </c>
       <c r="B62" s="17">
-        <v>105100</v>
+        <v>105400</v>
       </c>
       <c r="C62" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
+    </row>
+    <row r="63" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A63" s="2">
+        <v>5054002</v>
+      </c>
+      <c r="B63" s="17">
+        <v>105400</v>
+      </c>
+      <c r="C63" t="s">
+        <v>158</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A64" s="2">
+        <v>5008001</v>
+      </c>
+      <c r="B64" s="17">
+        <v>100800</v>
+      </c>
+      <c r="C64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A65" s="2">
+        <v>5008002</v>
+      </c>
+      <c r="B65" s="17">
+        <v>100800</v>
+      </c>
+      <c r="C65" t="s">
+        <v>162</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A66" s="2">
+        <v>5053001</v>
+      </c>
+      <c r="B66" s="17">
+        <v>105300</v>
+      </c>
+      <c r="C66" t="s">
+        <v>167</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A67" s="2">
+        <v>5053002</v>
+      </c>
+      <c r="B67" s="17">
+        <v>105300</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" s="1">
+        <v>5</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A68" s="2">
+        <v>5057001</v>
+      </c>
+      <c r="B68" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C68" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A69" s="2">
+        <v>5057002</v>
+      </c>
+      <c r="B69" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C69" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A70" s="2">
+        <v>5057003</v>
+      </c>
+      <c r="B70" s="17">
+        <v>105700</v>
+      </c>
+      <c r="C70" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>172</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A71" s="2">
+        <v>5058001</v>
+      </c>
+      <c r="B71" s="17">
+        <v>105800</v>
+      </c>
+      <c r="C71" t="s">
+        <v>175</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A72" s="2">
+        <v>5058002</v>
+      </c>
+      <c r="B72" s="17">
+        <v>105800</v>
+      </c>
+      <c r="C72" t="s">
+        <v>175</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2">
@@ -3401,24 +3714,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3426,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3440,13 +3753,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3454,13 +3767,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3468,13 +3781,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3482,13 +3795,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3496,13 +3809,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3510,7 +3823,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3518,7 +3831,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3526,7 +3839,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3534,7 +3847,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3542,7 +3855,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3550,7 +3863,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3558,7 +3871,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3566,7 +3879,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3574,7 +3887,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3582,7 +3895,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3590,7 +3903,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3598,7 +3911,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3606,7 +3919,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3614,7 +3927,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3622,7 +3935,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3630,7 +3943,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3638,7 +3951,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3646,7 +3959,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3654,7 +3967,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3662,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3670,7 +3983,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3678,7 +3991,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3686,7 +3999,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3694,7 +4007,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3702,7 +4015,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3710,7 +4023,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3718,7 +4031,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3726,7 +4039,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3734,7 +4047,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3742,7 +4055,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3750,7 +4063,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3758,7 +4071,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3766,7 +4079,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3774,7 +4087,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3782,7 +4095,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3790,7 +4103,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3798,7 +4111,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3806,7 +4119,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3814,7 +4127,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3822,7 +4135,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
